--- a/EXCELL/listado-actualizado.xlsx
+++ b/EXCELL/listado-actualizado.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="848">
   <si>
     <t>Listado de Precios de Artículos</t>
   </si>
@@ -1150,12 +1150,6 @@
     <t>CUMPLE VELA TORCIONADA COLORES</t>
   </si>
   <si>
-    <t>DISPONIBLE</t>
-  </si>
-  <si>
-    <t>DSIPONIBLE</t>
-  </si>
-  <si>
     <t>EMBLOCADA 15X25 1/2KG</t>
   </si>
   <si>
@@ -2557,7 +2551,7 @@
     <t>VELAS LED COLOR</t>
   </si>
   <si>
-    <t>NUEVO PABLO</t>
+    <t xml:space="preserve">NUEVO ROSARIO </t>
   </si>
   <si>
     <t>}</t>
@@ -2651,7 +2645,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2675,6 +2669,9 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -8165,390 +8162,444 @@
         <v>379</v>
       </c>
       <c r="B379" s="6">
-        <v>361.9</v>
-      </c>
-      <c r="C379" s="6"/>
+        <v>1000.0</v>
+      </c>
+      <c r="C379" s="6">
+        <v>850.0</v>
+      </c>
       <c r="D379" s="7">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B380" s="6">
-        <v>207.6</v>
-      </c>
-      <c r="C380" s="6"/>
+        <v>1330.0</v>
+      </c>
+      <c r="C380" s="6">
+        <v>1235.0</v>
+      </c>
       <c r="D380" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B381" s="6">
-        <v>169.9</v>
-      </c>
-      <c r="C381" s="6"/>
+        <v>2100.0</v>
+      </c>
+      <c r="C381" s="6">
+        <v>1950.0</v>
+      </c>
       <c r="D381" s="7">
         <v>3.0</v>
       </c>
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B382" s="6">
-        <v>24.5</v>
-      </c>
-      <c r="C382" s="6"/>
+        <v>2660.0</v>
+      </c>
+      <c r="C382" s="6">
+        <v>2470.0</v>
+      </c>
       <c r="D382" s="7">
-        <v>25.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B383" s="6">
-        <v>453.0</v>
-      </c>
-      <c r="C383" s="6"/>
+        <v>3780.0</v>
+      </c>
+      <c r="C383" s="6">
+        <v>3510.0</v>
+      </c>
       <c r="D383" s="7">
         <v>3.0</v>
       </c>
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="5" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B384" s="6">
-        <v>229.3</v>
-      </c>
-      <c r="C384" s="6"/>
+        <v>5390.0</v>
+      </c>
+      <c r="C384" s="6">
+        <v>5005.0</v>
+      </c>
       <c r="D384" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="5" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B385" s="6">
-        <v>243.9</v>
-      </c>
-      <c r="C385" s="6"/>
+        <v>122.8</v>
+      </c>
+      <c r="C385" s="6">
+        <v>102.3</v>
+      </c>
       <c r="D385" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="5" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B386" s="6">
-        <v>243.9</v>
-      </c>
-      <c r="C386" s="6"/>
+        <v>350.4</v>
+      </c>
+      <c r="C386" s="6">
+        <v>336.4</v>
+      </c>
       <c r="D386" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="5" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B387" s="6">
-        <v>241.6</v>
-      </c>
-      <c r="C387" s="6"/>
+        <v>199.2</v>
+      </c>
+      <c r="C387" s="6">
+        <v>186.0</v>
+      </c>
       <c r="D387" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="5" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B388" s="6">
-        <v>213.6</v>
-      </c>
-      <c r="C388" s="6"/>
+        <v>109.7</v>
+      </c>
+      <c r="C388" s="6">
+        <v>80.8</v>
+      </c>
       <c r="D388" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="5" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B389" s="6">
-        <v>183.1</v>
-      </c>
-      <c r="C389" s="6"/>
+        <v>39.3</v>
+      </c>
+      <c r="C389" s="6">
+        <v>37.0</v>
+      </c>
       <c r="D389" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="5" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B390" s="6">
-        <v>1260.0</v>
-      </c>
-      <c r="C390" s="6"/>
+        <v>105.3</v>
+      </c>
+      <c r="C390" s="6">
+        <v>99.2</v>
+      </c>
       <c r="D390" s="7">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="5" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B391" s="6">
-        <v>190.5</v>
-      </c>
-      <c r="C391" s="6"/>
+        <v>231.9</v>
+      </c>
+      <c r="C391" s="6">
+        <v>217.4</v>
+      </c>
       <c r="D391" s="7">
         <v>5.0</v>
       </c>
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="5" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="B392" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="C392" s="6"/>
+        <v>571.2</v>
+      </c>
+      <c r="C392" s="6">
+        <v>535.6</v>
+      </c>
       <c r="D392" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="5" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B393" s="6">
-        <v>22.6</v>
-      </c>
-      <c r="C393" s="6"/>
+        <v>1423.0</v>
+      </c>
+      <c r="C393" s="6">
+        <v>1321.3</v>
+      </c>
       <c r="D393" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="5" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="B394" s="6">
-        <v>868.3</v>
-      </c>
-      <c r="C394" s="6"/>
+        <v>2102.1</v>
+      </c>
+      <c r="C394" s="6">
+        <v>1940.4</v>
+      </c>
       <c r="D394" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="5" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="B395" s="6">
-        <v>171.7</v>
-      </c>
-      <c r="C395" s="6"/>
+        <v>2782.4</v>
+      </c>
+      <c r="C395" s="6">
+        <v>2596.8</v>
+      </c>
       <c r="D395" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="5" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="B396" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="C396" s="6"/>
+        <v>2637.0</v>
+      </c>
+      <c r="C396" s="6">
+        <v>2526.9</v>
+      </c>
       <c r="D396" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="5" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B397" s="6">
-        <v>389.9</v>
-      </c>
-      <c r="C397" s="6"/>
+        <v>4147.0</v>
+      </c>
+      <c r="C397" s="6">
+        <v>3941.3</v>
+      </c>
       <c r="D397" s="7">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="5" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="B398" s="6">
-        <v>226.5</v>
-      </c>
-      <c r="C398" s="6"/>
+        <v>154.8</v>
+      </c>
+      <c r="C398" s="6">
+        <v>147.2</v>
+      </c>
       <c r="D398" s="7">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="5" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="B399" s="6">
-        <v>169.9</v>
-      </c>
-      <c r="C399" s="6"/>
+        <v>1200.0</v>
+      </c>
+      <c r="C399" s="6">
+        <v>1000.0</v>
+      </c>
       <c r="D399" s="7">
         <v>3.0</v>
       </c>
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="5" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="B400" s="6">
-        <v>169.9</v>
-      </c>
-      <c r="C400" s="6"/>
+        <v>1500.0</v>
+      </c>
+      <c r="C400" s="6">
+        <v>1400.0</v>
+      </c>
       <c r="D400" s="7">
         <v>3.0</v>
       </c>
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="5" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="B401" s="6">
-        <v>4.9</v>
-      </c>
-      <c r="C401" s="6"/>
+        <v>308.7</v>
+      </c>
+      <c r="C401" s="6">
+        <v>297.7</v>
+      </c>
       <c r="D401" s="7">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="5" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="B402" s="6">
-        <v>151.0</v>
-      </c>
-      <c r="C402" s="6"/>
+        <v>279.3</v>
+      </c>
+      <c r="C402" s="6">
+        <v>269.3</v>
+      </c>
       <c r="D402" s="7">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="5" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="B403" s="6">
-        <v>188.8</v>
-      </c>
-      <c r="C403" s="6"/>
+        <v>1102.5</v>
+      </c>
+      <c r="C403" s="6">
+        <v>1047.4</v>
+      </c>
       <c r="D403" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="5" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="B404" s="6">
-        <v>348.6</v>
-      </c>
-      <c r="C404" s="6"/>
+        <v>300.0</v>
+      </c>
+      <c r="C404" s="6">
+        <v>270.0</v>
+      </c>
       <c r="D404" s="7">
-        <v>20.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="5" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="B405" s="6">
-        <v>1996.5</v>
-      </c>
-      <c r="C405" s="6"/>
+        <v>700.0</v>
+      </c>
+      <c r="C405" s="6">
+        <v>600.0</v>
+      </c>
       <c r="D405" s="7">
         <v>3.0</v>
       </c>
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="5" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="B406" s="6">
-        <v>111.2</v>
+        <v>771.8</v>
       </c>
       <c r="C406" s="6">
-        <v>103.2</v>
+        <v>716.6</v>
       </c>
       <c r="D406" s="7">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="5" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="B407" s="6">
         <v>1000.0</v>
       </c>
       <c r="C407" s="6">
-        <v>850.0</v>
+        <v>900.0</v>
       </c>
       <c r="D407" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="5" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="B408" s="6">
-        <v>1330.0</v>
+        <v>3863.8</v>
       </c>
       <c r="C408" s="6">
-        <v>1235.0</v>
+        <v>3409.0</v>
       </c>
       <c r="D408" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="5" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="B409" s="6">
-        <v>2100.0</v>
+        <v>375.0</v>
       </c>
       <c r="C409" s="6">
-        <v>1950.0</v>
+        <v>343.8</v>
       </c>
       <c r="D409" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="5" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="B410" s="6">
-        <v>2660.0</v>
+        <v>1140.0</v>
       </c>
       <c r="C410" s="6">
-        <v>2470.0</v>
+        <v>1140.0</v>
       </c>
       <c r="D410" s="7">
         <v>3.0</v>
@@ -8556,13 +8607,13 @@
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="5" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="B411" s="6">
-        <v>3780.0</v>
+        <v>645.0</v>
       </c>
       <c r="C411" s="6">
-        <v>3510.0</v>
+        <v>645.0</v>
       </c>
       <c r="D411" s="7">
         <v>3.0</v>
@@ -8570,27 +8621,27 @@
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="5" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="B412" s="6">
-        <v>5390.0</v>
+        <v>3726.0</v>
       </c>
       <c r="C412" s="6">
-        <v>5005.0</v>
+        <v>3645.0</v>
       </c>
       <c r="D412" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="5" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="B413" s="6">
-        <v>122.8</v>
+        <v>4274.9</v>
       </c>
       <c r="C413" s="6">
-        <v>102.3</v>
+        <v>4393.8</v>
       </c>
       <c r="D413" s="7">
         <v>3.0</v>
@@ -8598,27 +8649,27 @@
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="5" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="B414" s="6">
-        <v>350.4</v>
+        <v>1000.0</v>
       </c>
       <c r="C414" s="6">
-        <v>336.4</v>
+        <v>900.0</v>
       </c>
       <c r="D414" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="5" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="B415" s="6">
-        <v>199.2</v>
+        <v>21000.0</v>
       </c>
       <c r="C415" s="6">
-        <v>186.0</v>
+        <v>19000.0</v>
       </c>
       <c r="D415" s="7">
         <v>2.0</v>
@@ -8626,293 +8677,291 @@
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="5" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="B416" s="6">
-        <v>109.7</v>
+        <v>4500.0</v>
       </c>
       <c r="C416" s="6">
-        <v>80.8</v>
+        <v>4000.0</v>
       </c>
       <c r="D416" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="5" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="B417" s="6">
-        <v>39.3</v>
+        <v>21000.0</v>
       </c>
       <c r="C417" s="6">
-        <v>37.0</v>
+        <v>21000.0</v>
       </c>
       <c r="D417" s="7">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="5" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="B418" s="6">
-        <v>105.3</v>
-      </c>
-      <c r="C418" s="6">
-        <v>99.2</v>
-      </c>
+        <v>9000.0</v>
+      </c>
+      <c r="C418" s="6"/>
       <c r="D418" s="7">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="5" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="B419" s="6">
-        <v>231.9</v>
+        <v>8800.0</v>
       </c>
       <c r="C419" s="6">
-        <v>217.4</v>
+        <v>8400.0</v>
       </c>
       <c r="D419" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="5" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="B420" s="6">
-        <v>571.2</v>
+        <v>9500.0</v>
       </c>
       <c r="C420" s="6">
-        <v>535.6</v>
+        <v>9000.0</v>
       </c>
       <c r="D420" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="5" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="B421" s="6">
-        <v>1423.0</v>
+        <v>1040.0</v>
       </c>
       <c r="C421" s="6">
-        <v>1321.3</v>
+        <v>1021.4</v>
       </c>
       <c r="D421" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="5" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="B422" s="6">
-        <v>2102.1</v>
+        <v>377.5</v>
       </c>
       <c r="C422" s="6">
-        <v>1940.4</v>
+        <v>358.6</v>
       </c>
       <c r="D422" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="5" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="B423" s="6">
-        <v>2782.4</v>
+        <v>236.2</v>
       </c>
       <c r="C423" s="6">
-        <v>2596.8</v>
+        <v>211.5</v>
       </c>
       <c r="D423" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="5" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="B424" s="6">
-        <v>2637.0</v>
+        <v>211.6</v>
       </c>
       <c r="C424" s="6">
-        <v>2526.9</v>
+        <v>191.2</v>
       </c>
       <c r="D424" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="5" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="B425" s="6">
-        <v>4147.0</v>
+        <v>684.5</v>
       </c>
       <c r="C425" s="6">
-        <v>3941.3</v>
+        <v>602.8</v>
       </c>
       <c r="D425" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="5" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="B426" s="6">
-        <v>154.8</v>
+        <v>2205.0</v>
       </c>
       <c r="C426" s="6">
-        <v>147.2</v>
+        <v>2205.0</v>
       </c>
       <c r="D426" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="5" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="B427" s="6">
-        <v>1200.0</v>
+        <v>495.9</v>
       </c>
       <c r="C427" s="6">
-        <v>1000.0</v>
+        <v>437.5</v>
       </c>
       <c r="D427" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="5" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B428" s="6">
-        <v>1500.0</v>
+        <v>255.0</v>
       </c>
       <c r="C428" s="6">
-        <v>1400.0</v>
+        <v>255.0</v>
       </c>
       <c r="D428" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="5" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="B429" s="6">
-        <v>308.7</v>
+        <v>223.1</v>
       </c>
       <c r="C429" s="6">
-        <v>297.7</v>
+        <v>196.9</v>
       </c>
       <c r="D429" s="7">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="5" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="B430" s="6">
-        <v>279.3</v>
+        <v>225.1</v>
       </c>
       <c r="C430" s="6">
-        <v>269.3</v>
+        <v>204.7</v>
       </c>
       <c r="D430" s="7">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="5" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B431" s="6">
-        <v>1102.5</v>
+        <v>386.4</v>
       </c>
       <c r="C431" s="6">
-        <v>1047.4</v>
+        <v>362.2</v>
       </c>
       <c r="D431" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="5" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="B432" s="6">
-        <v>300.0</v>
+        <v>391.0</v>
       </c>
       <c r="C432" s="6">
-        <v>270.0</v>
+        <v>345.0</v>
       </c>
       <c r="D432" s="7">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="5" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="B433" s="6">
-        <v>700.0</v>
+        <v>107.1</v>
       </c>
       <c r="C433" s="6">
-        <v>600.0</v>
+        <v>94.5</v>
       </c>
       <c r="D433" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="5" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B434" s="6">
-        <v>771.8</v>
+        <v>162.8</v>
       </c>
       <c r="C434" s="6">
-        <v>716.6</v>
+        <v>139.7</v>
       </c>
       <c r="D434" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="5" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="B435" s="6">
-        <v>1000.0</v>
+        <v>170.0</v>
       </c>
       <c r="C435" s="6">
-        <v>900.0</v>
+        <v>150.0</v>
       </c>
       <c r="D435" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="5" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="B436" s="6">
-        <v>3863.8</v>
+        <v>487.7</v>
       </c>
       <c r="C436" s="6">
-        <v>3409.0</v>
+        <v>433.6</v>
       </c>
       <c r="D436" s="7">
         <v>5.0</v>
@@ -8920,151 +8969,153 @@
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="5" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="B437" s="6">
-        <v>375.0</v>
+        <v>90.6</v>
       </c>
       <c r="C437" s="6">
-        <v>343.8</v>
+        <v>75.5</v>
       </c>
       <c r="D437" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="5" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="B438" s="6">
-        <v>1140.0</v>
+        <v>409.5</v>
       </c>
       <c r="C438" s="6">
-        <v>1140.0</v>
+        <v>382.2</v>
       </c>
       <c r="D438" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="5" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="B439" s="6">
-        <v>645.0</v>
+        <v>187.4</v>
       </c>
       <c r="C439" s="6">
-        <v>645.0</v>
+        <v>165.4</v>
       </c>
       <c r="D439" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="5" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="B440" s="6">
-        <v>3726.0</v>
+        <v>85.0</v>
       </c>
       <c r="C440" s="6">
-        <v>3645.0</v>
+        <v>75.0</v>
       </c>
       <c r="D440" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="5" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="B441" s="6">
-        <v>4274.9</v>
+        <v>83.2</v>
       </c>
       <c r="C441" s="6">
-        <v>4393.8</v>
+        <v>78.0</v>
       </c>
       <c r="D441" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="5" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="B442" s="6">
-        <v>1000.0</v>
+        <v>58.3</v>
       </c>
       <c r="C442" s="6">
-        <v>900.0</v>
+        <v>54.4</v>
       </c>
       <c r="D442" s="7">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="5" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="B443" s="6">
-        <v>21000.0</v>
+        <v>1400.0</v>
       </c>
       <c r="C443" s="6">
-        <v>19000.0</v>
+        <v>1400.0</v>
       </c>
       <c r="D443" s="7">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="5" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="B444" s="6">
-        <v>4500.0</v>
+        <v>172.8</v>
       </c>
       <c r="C444" s="6">
-        <v>4000.0</v>
+        <v>162.0</v>
       </c>
       <c r="D444" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="5" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="B445" s="6">
-        <v>21000.0</v>
+        <v>228.8</v>
       </c>
       <c r="C445" s="6">
-        <v>21000.0</v>
+        <v>204.3</v>
       </c>
       <c r="D445" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="5" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="B446" s="6">
-        <v>9000.0</v>
-      </c>
-      <c r="C446" s="6"/>
+        <v>322.3</v>
+      </c>
+      <c r="C446" s="6">
+        <v>284.4</v>
+      </c>
       <c r="D446" s="7">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="5" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="B447" s="6">
-        <v>8800.0</v>
+        <v>181.8</v>
       </c>
       <c r="C447" s="6">
-        <v>8400.0</v>
+        <v>160.4</v>
       </c>
       <c r="D447" s="7">
         <v>2.0</v>
@@ -9072,69 +9123,69 @@
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="5" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="B448" s="6">
-        <v>9500.0</v>
+        <v>270.0</v>
       </c>
       <c r="C448" s="6">
-        <v>9000.0</v>
+        <v>270.0</v>
       </c>
       <c r="D448" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="5" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="B449" s="6">
-        <v>1040.0</v>
+        <v>495.0</v>
       </c>
       <c r="C449" s="6">
-        <v>1021.4</v>
+        <v>495.0</v>
       </c>
       <c r="D449" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="5" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="B450" s="6">
-        <v>377.5</v>
+        <v>231.0</v>
       </c>
       <c r="C450" s="6">
-        <v>358.6</v>
+        <v>211.8</v>
       </c>
       <c r="D450" s="7">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="5" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="B451" s="6">
-        <v>236.2</v>
+        <v>294.7</v>
       </c>
       <c r="C451" s="6">
-        <v>211.5</v>
+        <v>270.1</v>
       </c>
       <c r="D451" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="5" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="B452" s="6">
-        <v>211.6</v>
+        <v>825.0</v>
       </c>
       <c r="C452" s="6">
-        <v>191.2</v>
+        <v>715.0</v>
       </c>
       <c r="D452" s="7">
         <v>5.0</v>
@@ -9142,27 +9193,27 @@
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="5" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="B453" s="6">
-        <v>684.5</v>
+        <v>736.4</v>
       </c>
       <c r="C453" s="6">
-        <v>602.8</v>
+        <v>736.4</v>
       </c>
       <c r="D453" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="5" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="B454" s="6">
-        <v>2205.0</v>
+        <v>151.0</v>
       </c>
       <c r="C454" s="6">
-        <v>2205.0</v>
+        <v>132.1</v>
       </c>
       <c r="D454" s="7">
         <v>5.0</v>
@@ -9170,55 +9221,55 @@
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="5" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="B455" s="6">
-        <v>495.9</v>
+        <v>120.0</v>
       </c>
       <c r="C455" s="6">
-        <v>437.5</v>
+        <v>120.0</v>
       </c>
       <c r="D455" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="5" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="B456" s="6">
-        <v>255.0</v>
+        <v>390.0</v>
       </c>
       <c r="C456" s="6">
-        <v>255.0</v>
+        <v>390.0</v>
       </c>
       <c r="D456" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="5" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B457" s="6">
-        <v>223.1</v>
+        <v>200.0</v>
       </c>
       <c r="C457" s="6">
-        <v>196.9</v>
+        <v>200.0</v>
       </c>
       <c r="D457" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="5" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="B458" s="6">
-        <v>225.1</v>
+        <v>7003.0</v>
       </c>
       <c r="C458" s="6">
-        <v>204.7</v>
+        <v>6486.0</v>
       </c>
       <c r="D458" s="7">
         <v>2.0</v>
@@ -9226,125 +9277,123 @@
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="5" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="B459" s="6">
-        <v>386.4</v>
+        <v>1500.0</v>
       </c>
       <c r="C459" s="6">
-        <v>362.2</v>
+        <v>1500.0</v>
       </c>
       <c r="D459" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="5" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="B460" s="6">
-        <v>391.0</v>
+        <v>800.0</v>
       </c>
       <c r="C460" s="6">
-        <v>345.0</v>
+        <v>800.0</v>
       </c>
       <c r="D460" s="7">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="5" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="B461" s="6">
-        <v>107.1</v>
+        <v>126.0</v>
       </c>
       <c r="C461" s="6">
-        <v>94.5</v>
+        <v>110.2</v>
       </c>
       <c r="D461" s="7">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="5" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="B462" s="6">
-        <v>162.8</v>
+        <v>171.1</v>
       </c>
       <c r="C462" s="6">
-        <v>139.7</v>
+        <v>149.7</v>
       </c>
       <c r="D462" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="5" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="B463" s="6">
-        <v>170.0</v>
+        <v>693.4</v>
       </c>
       <c r="C463" s="6">
-        <v>150.0</v>
+        <v>693.4</v>
       </c>
       <c r="D463" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="5" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="B464" s="6">
-        <v>487.7</v>
+        <v>369.5</v>
       </c>
       <c r="C464" s="6">
-        <v>433.6</v>
+        <v>340.3</v>
       </c>
       <c r="D464" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="5" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="B465" s="6">
-        <v>90.6</v>
-      </c>
-      <c r="C465" s="6">
-        <v>75.5</v>
-      </c>
+        <v>680.6</v>
+      </c>
+      <c r="C465" s="6"/>
       <c r="D465" s="7">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="5" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="B466" s="6">
-        <v>409.5</v>
+        <v>707.1</v>
       </c>
       <c r="C466" s="6">
-        <v>382.2</v>
+        <v>647.1</v>
       </c>
       <c r="D466" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="5" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="B467" s="6">
-        <v>187.4</v>
+        <v>918.8</v>
       </c>
       <c r="C467" s="6">
-        <v>165.4</v>
+        <v>853.2</v>
       </c>
       <c r="D467" s="7">
         <v>2.0</v>
@@ -9352,83 +9401,83 @@
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="5" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="B468" s="6">
-        <v>85.0</v>
+        <v>188.8</v>
       </c>
       <c r="C468" s="6">
-        <v>75.0</v>
+        <v>151.0</v>
       </c>
       <c r="D468" s="7">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="5" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="B469" s="6">
-        <v>83.2</v>
+        <v>11000.0</v>
       </c>
       <c r="C469" s="6">
-        <v>78.0</v>
+        <v>11000.0</v>
       </c>
       <c r="D469" s="7">
-        <v>50.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="5" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="B470" s="6">
-        <v>58.3</v>
+        <v>350.0</v>
       </c>
       <c r="C470" s="6">
-        <v>54.4</v>
+        <v>330.0</v>
       </c>
       <c r="D470" s="7">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="5" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="B471" s="6">
-        <v>1400.0</v>
+        <v>10617.8</v>
       </c>
       <c r="C471" s="6">
-        <v>1400.0</v>
+        <v>10224.5</v>
       </c>
       <c r="D471" s="7">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="5" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="B472" s="6">
-        <v>172.8</v>
+        <v>143.0</v>
       </c>
       <c r="C472" s="6">
-        <v>162.0</v>
+        <v>119.2</v>
       </c>
       <c r="D472" s="7">
-        <v>25.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="5" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="B473" s="6">
-        <v>228.8</v>
+        <v>1440.0</v>
       </c>
       <c r="C473" s="6">
-        <v>204.3</v>
+        <v>1440.0</v>
       </c>
       <c r="D473" s="7">
         <v>5.0</v>
@@ -9436,55 +9485,55 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="5" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B474" s="6">
-        <v>322.3</v>
+        <v>339.8</v>
       </c>
       <c r="C474" s="6">
-        <v>284.4</v>
+        <v>0.0</v>
       </c>
       <c r="D474" s="7">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="5" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="B475" s="6">
-        <v>181.8</v>
+        <v>249.5</v>
       </c>
       <c r="C475" s="6">
-        <v>160.4</v>
+        <v>268.7</v>
       </c>
       <c r="D475" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="5" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="B476" s="6">
-        <v>270.0</v>
+        <v>556.1</v>
       </c>
       <c r="C476" s="6">
-        <v>270.0</v>
+        <v>556.1</v>
       </c>
       <c r="D476" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="5" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="B477" s="6">
-        <v>495.0</v>
+        <v>517.5</v>
       </c>
       <c r="C477" s="6">
-        <v>495.0</v>
+        <v>480.6</v>
       </c>
       <c r="D477" s="7">
         <v>5.0</v>
@@ -9492,55 +9541,55 @@
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="5" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B478" s="6">
-        <v>231.0</v>
+        <v>360.2</v>
       </c>
       <c r="C478" s="6">
-        <v>211.8</v>
+        <v>354.4</v>
       </c>
       <c r="D478" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="5" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="B479" s="6">
-        <v>294.7</v>
+        <v>478.2</v>
       </c>
       <c r="C479" s="6">
-        <v>270.1</v>
+        <v>439.9</v>
       </c>
       <c r="D479" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="5" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="B480" s="6">
-        <v>825.0</v>
+        <v>490.8</v>
       </c>
       <c r="C480" s="6">
-        <v>715.0</v>
+        <v>471.9</v>
       </c>
       <c r="D480" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="5" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="B481" s="6">
-        <v>736.4</v>
+        <v>1200.0</v>
       </c>
       <c r="C481" s="6">
-        <v>736.4</v>
+        <v>1100.0</v>
       </c>
       <c r="D481" s="7">
         <v>5.0</v>
@@ -9548,27 +9597,27 @@
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="5" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="B482" s="6">
-        <v>151.0</v>
+        <v>510.0</v>
       </c>
       <c r="C482" s="6">
-        <v>132.1</v>
+        <v>472.9</v>
       </c>
       <c r="D482" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="5" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="B483" s="6">
-        <v>120.0</v>
+        <v>2500.0</v>
       </c>
       <c r="C483" s="6">
-        <v>120.0</v>
+        <v>2000.0</v>
       </c>
       <c r="D483" s="7">
         <v>3.0</v>
@@ -9576,136 +9625,128 @@
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="5" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="B484" s="6">
-        <v>390.0</v>
+        <v>1493.3</v>
       </c>
       <c r="C484" s="6">
-        <v>390.0</v>
+        <v>0.0</v>
       </c>
       <c r="D484" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="5" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="B485" s="6">
-        <v>200.0</v>
+        <v>1911.0</v>
       </c>
       <c r="C485" s="6">
-        <v>200.0</v>
+        <v>1774.5</v>
       </c>
       <c r="D485" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="5" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="B486" s="6">
-        <v>7003.0</v>
+        <v>2700.0</v>
       </c>
       <c r="C486" s="6">
-        <v>6486.0</v>
+        <v>2500.0</v>
       </c>
       <c r="D486" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="5" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="B487" s="6">
-        <v>1500.0</v>
+        <v>825.0</v>
       </c>
       <c r="C487" s="6">
-        <v>1500.0</v>
+        <v>825.0</v>
       </c>
       <c r="D487" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="5" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="B488" s="6">
-        <v>800.0</v>
+        <v>820.2</v>
       </c>
       <c r="C488" s="6">
-        <v>800.0</v>
+        <v>550.0</v>
       </c>
       <c r="D488" s="7">
-        <v>5.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="5" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="B489" s="6">
-        <v>126.0</v>
-      </c>
-      <c r="C489" s="6">
-        <v>110.2</v>
-      </c>
+        <v>2242.1</v>
+      </c>
+      <c r="C489" s="6"/>
       <c r="D489" s="7">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="5" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="B490" s="6">
-        <v>171.1</v>
-      </c>
-      <c r="C490" s="6">
-        <v>149.7</v>
-      </c>
+        <v>1300.0</v>
+      </c>
+      <c r="C490" s="6"/>
       <c r="D490" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="5" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="B491" s="6">
-        <v>693.4</v>
-      </c>
-      <c r="C491" s="6">
-        <v>693.4</v>
-      </c>
+        <v>715.0</v>
+      </c>
+      <c r="C491" s="6"/>
       <c r="D491" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="5" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="B492" s="6">
-        <v>369.5</v>
-      </c>
-      <c r="C492" s="6">
-        <v>340.3</v>
-      </c>
+        <v>801.8</v>
+      </c>
+      <c r="C492" s="6"/>
       <c r="D492" s="7">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="5" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="B493" s="6">
-        <v>680.6</v>
+        <v>2200.1</v>
       </c>
       <c r="C493" s="6"/>
       <c r="D493" s="7">
@@ -9714,153 +9755,153 @@
     </row>
     <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="5" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="B494" s="6">
-        <v>707.1</v>
+        <v>200.0</v>
       </c>
       <c r="C494" s="6">
-        <v>647.1</v>
+        <v>200.0</v>
       </c>
       <c r="D494" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="5" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="B495" s="6">
-        <v>918.8</v>
+        <v>450.0</v>
       </c>
       <c r="C495" s="6">
-        <v>853.2</v>
+        <v>400.2</v>
       </c>
       <c r="D495" s="7">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="5" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="B496" s="6">
-        <v>188.8</v>
+        <v>1060.7</v>
       </c>
       <c r="C496" s="6">
-        <v>151.0</v>
+        <v>1022.8</v>
       </c>
       <c r="D496" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="5" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="B497" s="6">
-        <v>11000.0</v>
+        <v>1380.0</v>
       </c>
       <c r="C497" s="6">
-        <v>11000.0</v>
+        <v>1380.0</v>
       </c>
       <c r="D497" s="7">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="5" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="B498" s="6">
-        <v>350.0</v>
+        <v>136.0</v>
       </c>
       <c r="C498" s="6">
-        <v>330.0</v>
+        <v>136.0</v>
       </c>
       <c r="D498" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="5" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="B499" s="6">
-        <v>10617.8</v>
+        <v>900.0</v>
       </c>
       <c r="C499" s="6">
-        <v>10224.5</v>
+        <v>900.0</v>
       </c>
       <c r="D499" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="5" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="B500" s="6">
-        <v>143.0</v>
+        <v>2796.3</v>
       </c>
       <c r="C500" s="6">
-        <v>119.2</v>
+        <v>2313.6</v>
       </c>
       <c r="D500" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="5" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="B501" s="6">
-        <v>1440.0</v>
+        <v>2520.1</v>
       </c>
       <c r="C501" s="6">
-        <v>1440.0</v>
+        <v>2240.1</v>
       </c>
       <c r="D501" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="5" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="B502" s="6">
-        <v>339.8</v>
+        <v>2500.0</v>
       </c>
       <c r="C502" s="6">
-        <v>0.0</v>
+        <v>1562.5</v>
       </c>
       <c r="D502" s="7">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="5" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B503" s="6">
-        <v>249.5</v>
+        <v>281.2</v>
       </c>
       <c r="C503" s="6">
-        <v>268.7</v>
+        <v>256.5</v>
       </c>
       <c r="D503" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="5" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="B504" s="6">
-        <v>556.1</v>
+        <v>493.0</v>
       </c>
       <c r="C504" s="6">
-        <v>556.1</v>
+        <v>459.0</v>
       </c>
       <c r="D504" s="7">
         <v>3.0</v>
@@ -9868,27 +9909,27 @@
     </row>
     <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="5" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="B505" s="6">
-        <v>517.5</v>
+        <v>838.1</v>
       </c>
       <c r="C505" s="6">
-        <v>480.6</v>
+        <v>780.3</v>
       </c>
       <c r="D505" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="5" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="B506" s="6">
-        <v>360.2</v>
+        <v>210.0</v>
       </c>
       <c r="C506" s="6">
-        <v>354.4</v>
+        <v>190.0</v>
       </c>
       <c r="D506" s="7">
         <v>3.0</v>
@@ -9896,13 +9937,13 @@
     </row>
     <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="5" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="B507" s="6">
-        <v>478.2</v>
+        <v>476.6</v>
       </c>
       <c r="C507" s="6">
-        <v>439.9</v>
+        <v>434.7</v>
       </c>
       <c r="D507" s="7">
         <v>3.0</v>
@@ -9910,255 +9951,265 @@
     </row>
     <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="5" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="B508" s="6">
-        <v>490.8</v>
+        <v>180.0</v>
       </c>
       <c r="C508" s="6">
-        <v>471.9</v>
+        <v>170.0</v>
       </c>
       <c r="D508" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="5" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="B509" s="6">
-        <v>1200.0</v>
+        <v>3000.0</v>
       </c>
       <c r="C509" s="6">
-        <v>1100.0</v>
+        <v>2600.0</v>
       </c>
       <c r="D509" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="5" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="B510" s="6">
-        <v>510.0</v>
+        <v>660.7</v>
       </c>
       <c r="C510" s="6">
-        <v>472.9</v>
+        <v>613.5</v>
       </c>
       <c r="D510" s="7">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="5" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="B511" s="6">
-        <v>2500.0</v>
+        <v>594.6</v>
       </c>
       <c r="C511" s="6">
-        <v>2000.0</v>
+        <v>552.1</v>
       </c>
       <c r="D511" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="5" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
       <c r="B512" s="6">
-        <v>1493.3</v>
+        <v>2000.0</v>
       </c>
       <c r="C512" s="6">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="D512" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="5" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="B513" s="6">
-        <v>1911.0</v>
+        <v>1800.0</v>
       </c>
       <c r="C513" s="6">
-        <v>1774.5</v>
+        <v>1800.0</v>
       </c>
       <c r="D513" s="7">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="5" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="B514" s="6">
-        <v>2700.0</v>
+        <v>150.0</v>
       </c>
       <c r="C514" s="6">
-        <v>2500.0</v>
+        <v>150.0</v>
       </c>
       <c r="D514" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="5" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="B515" s="6">
-        <v>825.0</v>
+        <v>590.6</v>
       </c>
       <c r="C515" s="6">
-        <v>825.0</v>
+        <v>551.2</v>
       </c>
       <c r="D515" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="5" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="B516" s="6">
-        <v>820.2</v>
+        <v>3333.0</v>
       </c>
       <c r="C516" s="6">
-        <v>550.0</v>
+        <v>3333.0</v>
       </c>
       <c r="D516" s="7">
-        <v>24.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="5" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="B517" s="6">
-        <v>2242.1</v>
-      </c>
-      <c r="C517" s="6"/>
+        <v>1092.0</v>
+      </c>
+      <c r="C517" s="6">
+        <v>1092.0</v>
+      </c>
       <c r="D517" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="5" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="B518" s="6">
-        <v>1300.0</v>
-      </c>
-      <c r="C518" s="6"/>
+        <v>210.0</v>
+      </c>
+      <c r="C518" s="6">
+        <v>210.0</v>
+      </c>
       <c r="D518" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="5" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="B519" s="6">
-        <v>715.0</v>
-      </c>
-      <c r="C519" s="6"/>
+        <v>3450.0</v>
+      </c>
+      <c r="C519" s="6">
+        <v>3450.0</v>
+      </c>
       <c r="D519" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="5" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="B520" s="6">
-        <v>801.8</v>
-      </c>
-      <c r="C520" s="6"/>
+        <v>1080.0</v>
+      </c>
+      <c r="C520" s="6">
+        <v>1080.0</v>
+      </c>
       <c r="D520" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="5" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="B521" s="6">
-        <v>2200.1</v>
-      </c>
-      <c r="C521" s="6"/>
+        <v>592.0</v>
+      </c>
+      <c r="C521" s="6">
+        <v>592.0</v>
+      </c>
       <c r="D521" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="5" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="B522" s="6">
-        <v>200.0</v>
+        <v>512.4</v>
       </c>
       <c r="C522" s="6">
-        <v>200.0</v>
+        <v>512.4</v>
       </c>
       <c r="D522" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="5" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="B523" s="6">
-        <v>450.0</v>
+        <v>630.0</v>
       </c>
       <c r="C523" s="6">
-        <v>400.2</v>
+        <v>630.0</v>
       </c>
       <c r="D523" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="5" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="B524" s="6">
-        <v>1060.7</v>
+        <v>935.0</v>
       </c>
       <c r="C524" s="6">
-        <v>1022.8</v>
+        <v>935.0</v>
       </c>
       <c r="D524" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="5" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="B525" s="6">
-        <v>1380.0</v>
+        <v>262.5</v>
       </c>
       <c r="C525" s="6">
-        <v>1380.0</v>
+        <v>236.2</v>
       </c>
       <c r="D525" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="5" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="B526" s="6">
-        <v>136.0</v>
+        <v>1000.0</v>
       </c>
       <c r="C526" s="6">
-        <v>136.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D526" s="7">
         <v>10.0</v>
@@ -10166,237 +10217,237 @@
     </row>
     <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="5" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="B527" s="6">
-        <v>900.0</v>
+        <v>158.5</v>
       </c>
       <c r="C527" s="6">
-        <v>900.0</v>
+        <v>136.1</v>
       </c>
       <c r="D527" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="5" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="B528" s="6">
-        <v>2796.3</v>
+        <v>5000.0</v>
       </c>
       <c r="C528" s="6">
-        <v>2313.6</v>
+        <v>0.0</v>
       </c>
       <c r="D528" s="7">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="5" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="B529" s="6">
-        <v>2520.1</v>
+        <v>274.1</v>
       </c>
       <c r="C529" s="6">
-        <v>2240.1</v>
+        <v>263.6</v>
       </c>
       <c r="D529" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="5" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="B530" s="6">
-        <v>2500.0</v>
+        <v>289.0</v>
       </c>
       <c r="C530" s="6">
-        <v>1562.5</v>
+        <v>277.9</v>
       </c>
       <c r="D530" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="5" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="B531" s="6">
-        <v>281.2</v>
+        <v>303.8</v>
       </c>
       <c r="C531" s="6">
-        <v>256.5</v>
+        <v>292.1</v>
       </c>
       <c r="D531" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="5" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="B532" s="6">
-        <v>493.0</v>
+        <v>333.0</v>
       </c>
       <c r="C532" s="6">
-        <v>459.0</v>
+        <v>310.8</v>
       </c>
       <c r="D532" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="5" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="B533" s="6">
-        <v>838.1</v>
+        <v>202.5</v>
       </c>
       <c r="C533" s="6">
-        <v>780.3</v>
+        <v>189.0</v>
       </c>
       <c r="D533" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="5" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="B534" s="6">
+        <v>225.0</v>
+      </c>
+      <c r="C534" s="6">
         <v>210.0</v>
       </c>
-      <c r="C534" s="6">
-        <v>190.0</v>
-      </c>
       <c r="D534" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="5" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="B535" s="6">
-        <v>476.6</v>
+        <v>165.0</v>
       </c>
       <c r="C535" s="6">
-        <v>434.7</v>
+        <v>152.9</v>
       </c>
       <c r="D535" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="5" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="B536" s="6">
-        <v>180.0</v>
+        <v>31.5</v>
       </c>
       <c r="C536" s="6">
-        <v>170.0</v>
+        <v>634.7</v>
       </c>
       <c r="D536" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="5" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="B537" s="6">
-        <v>3000.0</v>
+        <v>683.5</v>
       </c>
       <c r="C537" s="6">
-        <v>2600.0</v>
+        <v>634.7</v>
       </c>
       <c r="D537" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="5" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="B538" s="6">
-        <v>660.7</v>
+        <v>683.5</v>
       </c>
       <c r="C538" s="6">
-        <v>613.5</v>
+        <v>634.7</v>
       </c>
       <c r="D538" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="5" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="B539" s="6">
-        <v>594.6</v>
+        <v>651.0</v>
       </c>
       <c r="C539" s="6">
-        <v>552.1</v>
+        <v>604.5</v>
       </c>
       <c r="D539" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="5" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="B540" s="6">
-        <v>2000.0</v>
+        <v>683.5</v>
       </c>
       <c r="C540" s="6">
-        <v>1700.0</v>
+        <v>634.7</v>
       </c>
       <c r="D540" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="5" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="B541" s="6">
-        <v>1800.0</v>
+        <v>683.5</v>
       </c>
       <c r="C541" s="6">
-        <v>1800.0</v>
+        <v>634.7</v>
       </c>
       <c r="D541" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="5" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="B542" s="6">
-        <v>150.0</v>
+        <v>683.5</v>
       </c>
       <c r="C542" s="6">
-        <v>150.0</v>
+        <v>634.7</v>
       </c>
       <c r="D542" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="5" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="B543" s="6">
-        <v>590.6</v>
+        <v>683.5</v>
       </c>
       <c r="C543" s="6">
-        <v>551.2</v>
+        <v>634.7</v>
       </c>
       <c r="D543" s="7">
         <v>5.0</v>
@@ -10404,13 +10455,13 @@
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="5" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="B544" s="6">
-        <v>3333.0</v>
+        <v>735.0</v>
       </c>
       <c r="C544" s="6">
-        <v>3333.0</v>
+        <v>682.5</v>
       </c>
       <c r="D544" s="7">
         <v>3.0</v>
@@ -10418,13 +10469,13 @@
     </row>
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="5" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="B545" s="6">
-        <v>1092.0</v>
+        <v>735.0</v>
       </c>
       <c r="C545" s="6">
-        <v>1092.0</v>
+        <v>682.5</v>
       </c>
       <c r="D545" s="7">
         <v>3.0</v>
@@ -10432,27 +10483,27 @@
     </row>
     <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="5" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="B546" s="6">
-        <v>210.0</v>
+        <v>735.0</v>
       </c>
       <c r="C546" s="6">
-        <v>210.0</v>
+        <v>682.5</v>
       </c>
       <c r="D546" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="5" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="B547" s="6">
-        <v>3450.0</v>
+        <v>735.0</v>
       </c>
       <c r="C547" s="6">
-        <v>3450.0</v>
+        <v>682.5</v>
       </c>
       <c r="D547" s="7">
         <v>3.0</v>
@@ -10460,13 +10511,13 @@
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="5" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="B548" s="6">
-        <v>1080.0</v>
+        <v>735.0</v>
       </c>
       <c r="C548" s="6">
-        <v>1080.0</v>
+        <v>682.5</v>
       </c>
       <c r="D548" s="7">
         <v>3.0</v>
@@ -10474,125 +10525,125 @@
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="5" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="B549" s="6">
-        <v>592.0</v>
+        <v>153.9</v>
       </c>
       <c r="C549" s="6">
-        <v>592.0</v>
+        <v>142.5</v>
       </c>
       <c r="D549" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="5" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="B550" s="6">
-        <v>512.4</v>
+        <v>101.3</v>
       </c>
       <c r="C550" s="6">
-        <v>512.4</v>
+        <v>93.8</v>
       </c>
       <c r="D550" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="5" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="B551" s="6">
-        <v>630.0</v>
+        <v>102.6</v>
       </c>
       <c r="C551" s="6">
-        <v>630.0</v>
+        <v>95.0</v>
       </c>
       <c r="D551" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="5" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="B552" s="6">
-        <v>935.0</v>
+        <v>175.5</v>
       </c>
       <c r="C552" s="6">
-        <v>935.0</v>
+        <v>162.5</v>
       </c>
       <c r="D552" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="5" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="B553" s="6">
-        <v>262.5</v>
+        <v>186.3</v>
       </c>
       <c r="C553" s="6">
-        <v>236.2</v>
+        <v>178.2</v>
       </c>
       <c r="D553" s="7">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="5" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="B554" s="6">
-        <v>1000.0</v>
+        <v>243.0</v>
       </c>
       <c r="C554" s="6">
-        <v>1000.0</v>
+        <v>225.0</v>
       </c>
       <c r="D554" s="7">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="5" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="B555" s="6">
-        <v>158.5</v>
+        <v>331.5</v>
       </c>
       <c r="C555" s="6">
-        <v>136.1</v>
+        <v>318.8</v>
       </c>
       <c r="D555" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="5" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="B556" s="6">
-        <v>5000.0</v>
+        <v>339.3</v>
       </c>
       <c r="C556" s="6">
-        <v>0.0</v>
+        <v>326.2</v>
       </c>
       <c r="D556" s="7">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="5" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="B557" s="6">
-        <v>274.1</v>
+        <v>353.6</v>
       </c>
       <c r="C557" s="6">
-        <v>263.6</v>
+        <v>340.0</v>
       </c>
       <c r="D557" s="7">
         <v>10.0</v>
@@ -10600,13 +10651,13 @@
     </row>
     <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="5" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="B558" s="6">
-        <v>289.0</v>
+        <v>29.5</v>
       </c>
       <c r="C558" s="6">
-        <v>277.9</v>
+        <v>27.8</v>
       </c>
       <c r="D558" s="7">
         <v>10.0</v>
@@ -10614,13 +10665,13 @@
     </row>
     <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="5" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="B559" s="6">
-        <v>303.8</v>
+        <v>55.5</v>
       </c>
       <c r="C559" s="6">
-        <v>292.1</v>
+        <v>51.8</v>
       </c>
       <c r="D559" s="7">
         <v>10.0</v>
@@ -10628,13 +10679,13 @@
     </row>
     <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="5" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="B560" s="6">
-        <v>333.0</v>
+        <v>70.5</v>
       </c>
       <c r="C560" s="6">
-        <v>310.8</v>
+        <v>65.8</v>
       </c>
       <c r="D560" s="7">
         <v>10.0</v>
@@ -10642,13 +10693,13 @@
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="5" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="B561" s="6">
-        <v>202.5</v>
+        <v>37.5</v>
       </c>
       <c r="C561" s="6">
-        <v>189.0</v>
+        <v>35.0</v>
       </c>
       <c r="D561" s="7">
         <v>10.0</v>
@@ -10656,13 +10707,13 @@
     </row>
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="5" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="B562" s="6">
-        <v>225.0</v>
+        <v>57.0</v>
       </c>
       <c r="C562" s="6">
-        <v>210.0</v>
+        <v>53.2</v>
       </c>
       <c r="D562" s="7">
         <v>10.0</v>
@@ -10670,13 +10721,13 @@
     </row>
     <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="5" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="B563" s="6">
-        <v>165.0</v>
+        <v>70.5</v>
       </c>
       <c r="C563" s="6">
-        <v>152.9</v>
+        <v>65.8</v>
       </c>
       <c r="D563" s="7">
         <v>10.0</v>
@@ -10684,27 +10735,27 @@
     </row>
     <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="5" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="B564" s="6">
-        <v>31.5</v>
+        <v>51.0</v>
       </c>
       <c r="C564" s="6">
-        <v>634.7</v>
+        <v>48.0</v>
       </c>
       <c r="D564" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="5" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="B565" s="6">
-        <v>683.5</v>
+        <v>52.5</v>
       </c>
       <c r="C565" s="6">
-        <v>634.7</v>
+        <v>49.0</v>
       </c>
       <c r="D565" s="7">
         <v>10.0</v>
@@ -10712,69 +10763,69 @@
     </row>
     <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="5" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="B566" s="6">
-        <v>683.5</v>
+        <v>61.5</v>
       </c>
       <c r="C566" s="6">
-        <v>634.7</v>
+        <v>58.2</v>
       </c>
       <c r="D566" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="5" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="B567" s="6">
-        <v>651.0</v>
+        <v>69.0</v>
       </c>
       <c r="C567" s="6">
-        <v>604.5</v>
+        <v>65.3</v>
       </c>
       <c r="D567" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="5" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="B568" s="6">
-        <v>683.5</v>
+        <v>3300.0</v>
       </c>
       <c r="C568" s="6">
-        <v>634.7</v>
+        <v>3300.0</v>
       </c>
       <c r="D568" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="5" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="B569" s="6">
-        <v>683.5</v>
+        <v>350.0</v>
       </c>
       <c r="C569" s="6">
-        <v>634.7</v>
+        <v>400.0</v>
       </c>
       <c r="D569" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="5" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="B570" s="6">
-        <v>683.5</v>
+        <v>2500.0</v>
       </c>
       <c r="C570" s="6">
-        <v>634.7</v>
+        <v>2300.0</v>
       </c>
       <c r="D570" s="7">
         <v>5.0</v>
@@ -10782,167 +10833,167 @@
     </row>
     <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="5" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="B571" s="6">
-        <v>683.5</v>
+        <v>43.6</v>
       </c>
       <c r="C571" s="6">
-        <v>634.7</v>
+        <v>40.5</v>
       </c>
       <c r="D571" s="7">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="5" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="B572" s="6">
-        <v>735.0</v>
+        <v>118.8</v>
       </c>
       <c r="C572" s="6">
-        <v>682.5</v>
+        <v>114.0</v>
       </c>
       <c r="D572" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="5" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="B573" s="6">
-        <v>735.0</v>
+        <v>205.0</v>
       </c>
       <c r="C573" s="6">
-        <v>682.5</v>
+        <v>201.6</v>
       </c>
       <c r="D573" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="5" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="B574" s="6">
-        <v>735.0</v>
+        <v>1000.0</v>
       </c>
       <c r="C574" s="6">
-        <v>682.5</v>
+        <v>1000.0</v>
       </c>
       <c r="D574" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="5" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="B575" s="6">
-        <v>735.0</v>
+        <v>2698.5</v>
       </c>
       <c r="C575" s="6">
-        <v>682.5</v>
+        <v>2698.5</v>
       </c>
       <c r="D575" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="5" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="B576" s="6">
-        <v>735.0</v>
+        <v>508.2</v>
       </c>
       <c r="C576" s="6">
-        <v>682.5</v>
+        <v>465.9</v>
       </c>
       <c r="D576" s="7">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="5" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="B577" s="6">
-        <v>153.9</v>
+        <v>2240.0</v>
       </c>
       <c r="C577" s="6">
-        <v>142.5</v>
+        <v>2112.0</v>
       </c>
       <c r="D577" s="7">
-        <v>25.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="5" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="B578" s="6">
-        <v>101.3</v>
+        <v>1804.5</v>
       </c>
       <c r="C578" s="6">
-        <v>93.8</v>
+        <v>1680.0</v>
       </c>
       <c r="D578" s="7">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="5" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="B579" s="6">
-        <v>102.6</v>
+        <v>1800.0</v>
       </c>
       <c r="C579" s="6">
-        <v>95.0</v>
+        <v>1680.0</v>
       </c>
       <c r="D579" s="7">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="5" t="s">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="B580" s="6">
-        <v>175.5</v>
+        <v>988.0</v>
       </c>
       <c r="C580" s="6">
-        <v>162.5</v>
+        <v>988.0</v>
       </c>
       <c r="D580" s="7">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="5" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="B581" s="6">
-        <v>186.3</v>
+        <v>826.0</v>
       </c>
       <c r="C581" s="6">
-        <v>178.2</v>
+        <v>826.0</v>
       </c>
       <c r="D581" s="7">
-        <v>25.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="5" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="B582" s="6">
-        <v>243.0</v>
+        <v>77.0</v>
       </c>
       <c r="C582" s="6">
-        <v>225.0</v>
+        <v>71.5</v>
       </c>
       <c r="D582" s="7">
         <v>25.0</v>
@@ -10950,41 +11001,41 @@
     </row>
     <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="5" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="B583" s="6">
-        <v>331.5</v>
+        <v>12.8</v>
       </c>
       <c r="C583" s="6">
-        <v>318.8</v>
+        <v>10.4</v>
       </c>
       <c r="D583" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="5" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="B584" s="6">
-        <v>339.3</v>
+        <v>15.6</v>
       </c>
       <c r="C584" s="6">
-        <v>326.2</v>
+        <v>12.6</v>
       </c>
       <c r="D584" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="5" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="B585" s="6">
-        <v>353.6</v>
+        <v>18.9</v>
       </c>
       <c r="C585" s="6">
-        <v>340.0</v>
+        <v>15.3</v>
       </c>
       <c r="D585" s="7">
         <v>10.0</v>
@@ -10992,363 +11043,359 @@
     </row>
     <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="5" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="B586" s="6">
-        <v>29.5</v>
+        <v>20.1</v>
       </c>
       <c r="C586" s="6">
-        <v>27.8</v>
+        <v>16.3</v>
       </c>
       <c r="D586" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="5" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="B587" s="6">
-        <v>55.5</v>
+        <v>25.2</v>
       </c>
       <c r="C587" s="6">
-        <v>51.8</v>
+        <v>20.5</v>
       </c>
       <c r="D587" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="5" t="s">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="B588" s="6">
-        <v>70.5</v>
+        <v>48.0</v>
       </c>
       <c r="C588" s="6">
-        <v>65.8</v>
+        <v>42.0</v>
       </c>
       <c r="D588" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="5" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="B589" s="6">
-        <v>37.5</v>
+        <v>39.7</v>
       </c>
       <c r="C589" s="6">
-        <v>35.0</v>
+        <v>32.2</v>
       </c>
       <c r="D589" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="5" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="B590" s="6">
-        <v>57.0</v>
+        <v>56.0</v>
       </c>
       <c r="C590" s="6">
-        <v>53.2</v>
+        <v>49.0</v>
       </c>
       <c r="D590" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="5" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="B591" s="6">
-        <v>70.5</v>
+        <v>52.8</v>
       </c>
       <c r="C591" s="6">
-        <v>65.8</v>
+        <v>41.2</v>
       </c>
       <c r="D591" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="5" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="B592" s="6">
-        <v>51.0</v>
+        <v>46.0</v>
       </c>
       <c r="C592" s="6">
-        <v>48.0</v>
+        <v>37.4</v>
       </c>
       <c r="D592" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="5" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="B593" s="6">
-        <v>52.5</v>
+        <v>76.8</v>
       </c>
       <c r="C593" s="6">
-        <v>49.0</v>
+        <v>67.2</v>
       </c>
       <c r="D593" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="5" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="B594" s="6">
-        <v>61.5</v>
+        <v>77.9</v>
       </c>
       <c r="C594" s="6">
-        <v>58.2</v>
+        <v>63.3</v>
       </c>
       <c r="D594" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="5" t="s">
-        <v>569</v>
+        <v>595</v>
       </c>
       <c r="B595" s="6">
-        <v>69.0</v>
+        <v>60.8</v>
       </c>
       <c r="C595" s="6">
-        <v>65.3</v>
+        <v>53.2</v>
       </c>
       <c r="D595" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="5" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="B596" s="6">
-        <v>3300.0</v>
+        <v>84.0</v>
       </c>
       <c r="C596" s="6">
-        <v>3300.0</v>
+        <v>68.2</v>
       </c>
       <c r="D596" s="7">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="5" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="B597" s="6">
-        <v>350.0</v>
+        <v>88.0</v>
       </c>
       <c r="C597" s="6">
-        <v>400.0</v>
+        <v>77.0</v>
       </c>
       <c r="D597" s="7">
-        <v>2.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="5" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="B598" s="6">
-        <v>2500.0</v>
+        <v>80.0</v>
       </c>
       <c r="C598" s="6">
-        <v>2300.0</v>
+        <v>70.0</v>
       </c>
       <c r="D598" s="7">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="5" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="B599" s="6">
-        <v>43.6</v>
+        <v>78.4</v>
       </c>
       <c r="C599" s="6">
-        <v>40.5</v>
+        <v>63.7</v>
       </c>
       <c r="D599" s="7">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="5" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="B600" s="6">
-        <v>118.8</v>
+        <v>81.5</v>
       </c>
       <c r="C600" s="6">
-        <v>114.0</v>
+        <v>66.2</v>
       </c>
       <c r="D600" s="7">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="5" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="B601" s="6">
-        <v>205.0</v>
+        <v>112.0</v>
       </c>
       <c r="C601" s="6">
-        <v>201.6</v>
+        <v>98.0</v>
       </c>
       <c r="D601" s="7">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="5" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="B602" s="6">
-        <v>1000.0</v>
+        <v>88.0</v>
       </c>
       <c r="C602" s="6">
-        <v>1000.0</v>
+        <v>77.0</v>
       </c>
       <c r="D602" s="7">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="5" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="B603" s="6">
-        <v>2698.5</v>
-      </c>
-      <c r="C603" s="6">
-        <v>2698.5</v>
-      </c>
+        <v>88.5</v>
+      </c>
+      <c r="C603" s="6"/>
       <c r="D603" s="7">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="5" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="B604" s="6">
-        <v>508.2</v>
+        <v>84.0</v>
       </c>
       <c r="C604" s="6">
-        <v>465.9</v>
+        <v>73.5</v>
       </c>
       <c r="D604" s="7">
-        <v>12.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="5" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="B605" s="6">
-        <v>2240.0</v>
-      </c>
-      <c r="C605" s="6">
-        <v>2112.0</v>
-      </c>
+        <v>71.9</v>
+      </c>
+      <c r="C605" s="6"/>
       <c r="D605" s="7">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="5" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="B606" s="6">
-        <v>1804.5</v>
+        <v>88.3</v>
       </c>
       <c r="C606" s="6">
-        <v>1680.0</v>
+        <v>86.4</v>
       </c>
       <c r="D606" s="7">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="5" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="B607" s="6">
-        <v>1800.0</v>
+        <v>132.8</v>
       </c>
       <c r="C607" s="6">
-        <v>1680.0</v>
+        <v>116.2</v>
       </c>
       <c r="D607" s="7">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="5" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="B608" s="6">
-        <v>988.0</v>
+        <v>15.5</v>
       </c>
       <c r="C608" s="6">
-        <v>988.0</v>
+        <v>12.5</v>
       </c>
       <c r="D608" s="7">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="5" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="B609" s="6">
-        <v>826.0</v>
+        <v>49.5</v>
       </c>
       <c r="C609" s="6">
-        <v>826.0</v>
+        <v>44.6</v>
       </c>
       <c r="D609" s="7">
-        <v>4.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="5" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="B610" s="6">
-        <v>77.0</v>
+        <v>44.5</v>
       </c>
       <c r="C610" s="6">
-        <v>71.5</v>
+        <v>40.1</v>
       </c>
       <c r="D610" s="7">
-        <v>25.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="5" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="B611" s="6">
-        <v>12.8</v>
+        <v>31.3</v>
       </c>
       <c r="C611" s="6">
-        <v>10.4</v>
+        <v>28.2</v>
       </c>
       <c r="D611" s="7">
         <v>100.0</v>
@@ -11356,13 +11403,13 @@
     </row>
     <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="5" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="B612" s="6">
-        <v>15.6</v>
+        <v>31.3</v>
       </c>
       <c r="C612" s="6">
-        <v>12.6</v>
+        <v>28.2</v>
       </c>
       <c r="D612" s="7">
         <v>100.0</v>
@@ -11370,471 +11417,475 @@
     </row>
     <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="5" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="B613" s="6">
-        <v>18.9</v>
+        <v>37.6</v>
       </c>
       <c r="C613" s="6">
-        <v>15.3</v>
+        <v>33.8</v>
       </c>
       <c r="D613" s="7">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="5" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="B614" s="6">
-        <v>20.1</v>
+        <v>242.0</v>
       </c>
       <c r="C614" s="6">
-        <v>16.3</v>
+        <v>125.8</v>
       </c>
       <c r="D614" s="7">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="5" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="B615" s="6">
-        <v>25.2</v>
+        <v>449.9</v>
       </c>
       <c r="C615" s="6">
-        <v>20.5</v>
+        <v>432.6</v>
       </c>
       <c r="D615" s="7">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="5" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="B616" s="6">
-        <v>48.0</v>
+        <v>450.0</v>
       </c>
       <c r="C616" s="6">
-        <v>42.0</v>
+        <v>450.0</v>
       </c>
       <c r="D616" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="5" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="B617" s="6">
-        <v>39.7</v>
+        <v>866.2</v>
       </c>
       <c r="C617" s="6">
-        <v>32.2</v>
+        <v>866.2</v>
       </c>
       <c r="D617" s="7">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="5" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="B618" s="6">
-        <v>56.0</v>
+        <v>1200.0</v>
       </c>
       <c r="C618" s="6">
-        <v>49.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D618" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="5" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="B619" s="6">
-        <v>52.8</v>
+        <v>565.5</v>
       </c>
       <c r="C619" s="6">
-        <v>41.2</v>
+        <v>565.5</v>
       </c>
       <c r="D619" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="5" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="B620" s="6">
-        <v>46.0</v>
+        <v>1712.2</v>
       </c>
       <c r="C620" s="6">
-        <v>37.4</v>
+        <v>1637.8</v>
       </c>
       <c r="D620" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="5" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="B621" s="6">
-        <v>76.8</v>
+        <v>600.0</v>
       </c>
       <c r="C621" s="6">
-        <v>67.2</v>
+        <v>560.0</v>
       </c>
       <c r="D621" s="7">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="5" t="s">
-        <v>596</v>
+        <v>620</v>
       </c>
       <c r="B622" s="6">
-        <v>77.9</v>
+        <v>94.4</v>
       </c>
       <c r="C622" s="6">
-        <v>63.3</v>
+        <v>84.9</v>
       </c>
       <c r="D622" s="7">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="5" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="B623" s="6">
-        <v>60.8</v>
+        <v>28.3</v>
       </c>
       <c r="C623" s="6">
-        <v>53.2</v>
+        <v>16.2</v>
       </c>
       <c r="D623" s="7">
-        <v>100.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="5" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="B624" s="6">
-        <v>84.0</v>
+        <v>200.0</v>
       </c>
       <c r="C624" s="6">
-        <v>68.2</v>
+        <v>190.0</v>
       </c>
       <c r="D624" s="7">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="5" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="B625" s="6">
-        <v>88.0</v>
+        <v>28.3</v>
       </c>
       <c r="C625" s="6">
-        <v>77.0</v>
+        <v>23.2</v>
       </c>
       <c r="D625" s="7">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="5" t="s">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="B626" s="6">
-        <v>80.0</v>
+        <v>48.6</v>
       </c>
       <c r="C626" s="6">
-        <v>70.0</v>
+        <v>43.2</v>
       </c>
       <c r="D626" s="7">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="5" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="B627" s="6">
-        <v>78.4</v>
+        <v>60.2</v>
       </c>
       <c r="C627" s="6">
-        <v>63.7</v>
+        <v>0.0</v>
       </c>
       <c r="D627" s="7">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="5" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="B628" s="6">
-        <v>81.5</v>
+        <v>99.3</v>
       </c>
       <c r="C628" s="6">
-        <v>66.2</v>
+        <v>0.0</v>
       </c>
       <c r="D628" s="7">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="5" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="B629" s="6">
-        <v>112.0</v>
+        <v>27.9</v>
       </c>
       <c r="C629" s="6">
-        <v>98.0</v>
+        <v>24.8</v>
       </c>
       <c r="D629" s="7">
-        <v>100.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="5" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="B630" s="6">
-        <v>88.0</v>
+        <v>1960.0</v>
       </c>
       <c r="C630" s="6">
-        <v>77.0</v>
+        <v>1820.0</v>
       </c>
       <c r="D630" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="5" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="B631" s="6">
-        <v>88.5</v>
-      </c>
-      <c r="C631" s="6"/>
+        <v>1960.0</v>
+      </c>
+      <c r="C631" s="6">
+        <v>1820.0</v>
+      </c>
       <c r="D631" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="5" t="s">
-        <v>605</v>
+        <v>630</v>
       </c>
       <c r="B632" s="6">
-        <v>84.0</v>
+        <v>1960.0</v>
       </c>
       <c r="C632" s="6">
-        <v>73.5</v>
+        <v>1820.0</v>
       </c>
       <c r="D632" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="5" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="B633" s="6">
-        <v>71.9</v>
-      </c>
-      <c r="C633" s="6"/>
+        <v>634.8</v>
+      </c>
+      <c r="C633" s="6">
+        <v>607.2</v>
+      </c>
       <c r="D633" s="7">
-        <v>100.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="5" t="s">
-        <v>606</v>
+        <v>632</v>
       </c>
       <c r="B634" s="6">
-        <v>88.3</v>
+        <v>1932.0</v>
       </c>
       <c r="C634" s="6">
-        <v>86.4</v>
+        <v>1848.0</v>
       </c>
       <c r="D634" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="5" t="s">
-        <v>607</v>
+        <v>633</v>
       </c>
       <c r="B635" s="6">
-        <v>132.8</v>
+        <v>9000.0</v>
       </c>
       <c r="C635" s="6">
-        <v>116.2</v>
+        <v>9000.0</v>
       </c>
       <c r="D635" s="7">
-        <v>100.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="5" t="s">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="B636" s="6">
-        <v>15.5</v>
+        <v>502.1</v>
       </c>
       <c r="C636" s="6">
-        <v>12.5</v>
+        <v>468.6</v>
       </c>
       <c r="D636" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="5" t="s">
-        <v>609</v>
+        <v>635</v>
       </c>
       <c r="B637" s="6">
-        <v>49.5</v>
+        <v>1040.0</v>
       </c>
       <c r="C637" s="6">
-        <v>44.6</v>
+        <v>1040.0</v>
       </c>
       <c r="D637" s="7">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="5" t="s">
-        <v>610</v>
+        <v>636</v>
       </c>
       <c r="B638" s="6">
-        <v>44.5</v>
+        <v>1029.2</v>
       </c>
       <c r="C638" s="6">
-        <v>40.1</v>
+        <v>955.7</v>
       </c>
       <c r="D638" s="7">
-        <v>100.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="5" t="s">
-        <v>611</v>
+        <v>637</v>
       </c>
       <c r="B639" s="6">
-        <v>31.3</v>
+        <v>1903.3</v>
       </c>
       <c r="C639" s="6">
-        <v>28.2</v>
+        <v>1865.2</v>
       </c>
       <c r="D639" s="7">
-        <v>100.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="5" t="s">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="B640" s="6">
-        <v>31.3</v>
+        <v>459.0</v>
       </c>
       <c r="C640" s="6">
-        <v>28.2</v>
+        <v>459.0</v>
       </c>
       <c r="D640" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="5" t="s">
-        <v>613</v>
+        <v>639</v>
       </c>
       <c r="B641" s="6">
-        <v>37.6</v>
+        <v>236.2</v>
       </c>
       <c r="C641" s="6">
-        <v>33.8</v>
+        <v>236.2</v>
       </c>
       <c r="D641" s="7">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="5" t="s">
-        <v>614</v>
+        <v>640</v>
       </c>
       <c r="B642" s="6">
-        <v>242.0</v>
+        <v>297.0</v>
       </c>
       <c r="C642" s="6">
-        <v>125.8</v>
+        <v>275.0</v>
       </c>
       <c r="D642" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="5" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="B643" s="6">
-        <v>449.9</v>
+        <v>267.1</v>
       </c>
       <c r="C643" s="6">
-        <v>432.6</v>
+        <v>242.9</v>
       </c>
       <c r="D643" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="5" t="s">
-        <v>616</v>
+        <v>642</v>
       </c>
       <c r="B644" s="6">
-        <v>450.0</v>
+        <v>650.0</v>
       </c>
       <c r="C644" s="6">
-        <v>450.0</v>
+        <v>600.0</v>
       </c>
       <c r="D644" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="5" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
       <c r="B645" s="6">
-        <v>866.2</v>
+        <v>237.5</v>
       </c>
       <c r="C645" s="6">
-        <v>866.2</v>
+        <v>197.9</v>
       </c>
       <c r="D645" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="5" t="s">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="B646" s="6">
-        <v>1200.0</v>
+        <v>2100.0</v>
       </c>
       <c r="C646" s="6">
-        <v>1000.0</v>
+        <v>2100.0</v>
       </c>
       <c r="D646" s="7">
         <v>3.0</v>
@@ -11842,13 +11893,13 @@
     </row>
     <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="5" t="s">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="B647" s="6">
-        <v>565.5</v>
+        <v>478.2</v>
       </c>
       <c r="C647" s="6">
-        <v>565.5</v>
+        <v>459.1</v>
       </c>
       <c r="D647" s="7">
         <v>3.0</v>
@@ -11856,237 +11907,231 @@
     </row>
     <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="5" t="s">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="B648" s="6">
-        <v>1712.2</v>
+        <v>960.0</v>
       </c>
       <c r="C648" s="6">
-        <v>1637.8</v>
+        <v>780.0</v>
       </c>
       <c r="D648" s="7">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="649" ht="15.75" customHeight="1">
       <c r="A649" s="5" t="s">
-        <v>621</v>
+        <v>647</v>
       </c>
       <c r="B649" s="6">
-        <v>600.0</v>
+        <v>526.8</v>
       </c>
       <c r="C649" s="6">
-        <v>560.0</v>
+        <v>449.2</v>
       </c>
       <c r="D649" s="7">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="5" t="s">
-        <v>622</v>
+        <v>648</v>
       </c>
       <c r="B650" s="6">
-        <v>94.4</v>
+        <v>528.0</v>
       </c>
       <c r="C650" s="6">
-        <v>84.9</v>
+        <v>495.0</v>
       </c>
       <c r="D650" s="7">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="5" t="s">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="B651" s="6">
-        <v>28.3</v>
+        <v>635.2</v>
       </c>
       <c r="C651" s="6">
-        <v>16.2</v>
+        <v>598.3</v>
       </c>
       <c r="D651" s="7">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="5" t="s">
-        <v>624</v>
+        <v>650</v>
       </c>
       <c r="B652" s="6">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="C652" s="6">
-        <v>190.0</v>
+        <v>225.0</v>
       </c>
       <c r="D652" s="7">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="5" t="s">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="B653" s="6">
-        <v>28.3</v>
+        <v>263.5</v>
       </c>
       <c r="C653" s="6">
-        <v>23.2</v>
+        <v>238.0</v>
       </c>
       <c r="D653" s="7">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="5" t="s">
-        <v>626</v>
+        <v>652</v>
       </c>
       <c r="B654" s="6">
-        <v>48.6</v>
+        <v>304.0</v>
       </c>
       <c r="C654" s="6">
-        <v>43.2</v>
+        <v>275.5</v>
       </c>
       <c r="D654" s="7">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="5" t="s">
-        <v>627</v>
+        <v>653</v>
       </c>
       <c r="B655" s="6">
-        <v>60.2</v>
+        <v>374.0</v>
       </c>
       <c r="C655" s="6">
-        <v>0.0</v>
+        <v>319.1</v>
       </c>
       <c r="D655" s="7">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="5" t="s">
-        <v>628</v>
+        <v>654</v>
       </c>
       <c r="B656" s="6">
-        <v>99.3</v>
+        <v>400.0</v>
       </c>
       <c r="C656" s="6">
-        <v>0.0</v>
+        <v>362.6</v>
       </c>
       <c r="D656" s="7">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="5" t="s">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="B657" s="6">
-        <v>27.9</v>
+        <v>480.0</v>
       </c>
       <c r="C657" s="6">
-        <v>24.8</v>
+        <v>450.0</v>
       </c>
       <c r="D657" s="7">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="5" t="s">
-        <v>630</v>
+        <v>656</v>
       </c>
       <c r="B658" s="6">
-        <v>1960.0</v>
-      </c>
-      <c r="C658" s="6">
-        <v>1820.0</v>
-      </c>
+        <v>6170.9</v>
+      </c>
+      <c r="C658" s="6"/>
       <c r="D658" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="5" t="s">
-        <v>631</v>
+        <v>657</v>
       </c>
       <c r="B659" s="6">
-        <v>1960.0</v>
-      </c>
-      <c r="C659" s="6">
-        <v>1820.0</v>
-      </c>
+        <v>240.0</v>
+      </c>
+      <c r="C659" s="6"/>
       <c r="D659" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="5" t="s">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="B660" s="6">
-        <v>1960.0</v>
-      </c>
-      <c r="C660" s="6">
-        <v>1820.0</v>
-      </c>
+        <v>370.0</v>
+      </c>
+      <c r="C660" s="6"/>
       <c r="D660" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="5" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="B661" s="6">
-        <v>634.8</v>
+        <v>300.0</v>
       </c>
       <c r="C661" s="6">
-        <v>607.2</v>
+        <v>300.0</v>
       </c>
       <c r="D661" s="7">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="5" t="s">
-        <v>634</v>
+        <v>660</v>
       </c>
       <c r="B662" s="6">
-        <v>1932.0</v>
+        <v>120.0</v>
       </c>
       <c r="C662" s="6">
-        <v>1848.0</v>
+        <v>105.0</v>
       </c>
       <c r="D662" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="5" t="s">
-        <v>635</v>
+        <v>661</v>
       </c>
       <c r="B663" s="6">
-        <v>9000.0</v>
+        <v>144.0</v>
       </c>
       <c r="C663" s="6">
-        <v>9000.0</v>
+        <v>134.5</v>
       </c>
       <c r="D663" s="7">
-        <v>25.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="5" t="s">
-        <v>636</v>
+        <v>662</v>
       </c>
       <c r="B664" s="6">
-        <v>502.1</v>
+        <v>105.0</v>
       </c>
       <c r="C664" s="6">
-        <v>468.6</v>
+        <v>98.0</v>
       </c>
       <c r="D664" s="7">
         <v>3.0</v>
@@ -12094,293 +12139,293 @@
     </row>
     <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="5" t="s">
-        <v>637</v>
+        <v>663</v>
       </c>
       <c r="B665" s="6">
-        <v>1040.0</v>
+        <v>16.1</v>
       </c>
       <c r="C665" s="6">
-        <v>1040.0</v>
+        <v>14.1</v>
       </c>
       <c r="D665" s="7">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="5" t="s">
-        <v>638</v>
+        <v>664</v>
       </c>
       <c r="B666" s="6">
-        <v>1029.2</v>
+        <v>1838.0</v>
       </c>
       <c r="C666" s="6">
-        <v>955.7</v>
+        <v>1671.1</v>
       </c>
       <c r="D666" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="5" t="s">
-        <v>639</v>
+        <v>665</v>
       </c>
       <c r="B667" s="6">
-        <v>1903.3</v>
+        <v>3517.7</v>
       </c>
       <c r="C667" s="6">
-        <v>1865.2</v>
+        <v>3220.3</v>
       </c>
       <c r="D667" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="5" t="s">
-        <v>640</v>
+        <v>666</v>
       </c>
       <c r="B668" s="6">
-        <v>459.0</v>
+        <v>475.7</v>
       </c>
       <c r="C668" s="6">
-        <v>459.0</v>
+        <v>441.7</v>
       </c>
       <c r="D668" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="5" t="s">
-        <v>641</v>
+        <v>667</v>
       </c>
       <c r="B669" s="6">
-        <v>236.2</v>
+        <v>900.0</v>
       </c>
       <c r="C669" s="6">
-        <v>236.2</v>
+        <v>800.0</v>
       </c>
       <c r="D669" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="5" t="s">
-        <v>642</v>
+        <v>668</v>
       </c>
       <c r="B670" s="6">
-        <v>297.0</v>
+        <v>750.0</v>
       </c>
       <c r="C670" s="6">
-        <v>275.0</v>
+        <v>680.0</v>
       </c>
       <c r="D670" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="5" t="s">
-        <v>643</v>
+        <v>669</v>
       </c>
       <c r="B671" s="6">
-        <v>267.1</v>
+        <v>281.2</v>
       </c>
       <c r="C671" s="6">
-        <v>242.9</v>
+        <v>258.4</v>
       </c>
       <c r="D671" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="5" t="s">
-        <v>644</v>
+        <v>670</v>
       </c>
       <c r="B672" s="6">
-        <v>650.0</v>
+        <v>518.0</v>
       </c>
       <c r="C672" s="6">
-        <v>600.0</v>
+        <v>476.0</v>
       </c>
       <c r="D672" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="5" t="s">
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="B673" s="6">
-        <v>237.5</v>
+        <v>560.0</v>
       </c>
       <c r="C673" s="6">
-        <v>197.9</v>
+        <v>520.0</v>
       </c>
       <c r="D673" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="5" t="s">
-        <v>646</v>
+        <v>672</v>
       </c>
       <c r="B674" s="6">
-        <v>2100.0</v>
+        <v>1476.9</v>
       </c>
       <c r="C674" s="6">
-        <v>2100.0</v>
+        <v>1357.2</v>
       </c>
       <c r="D674" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="5" t="s">
-        <v>647</v>
+        <v>673</v>
       </c>
       <c r="B675" s="6">
-        <v>478.2</v>
+        <v>2368.0</v>
       </c>
       <c r="C675" s="6">
-        <v>459.1</v>
+        <v>2176.0</v>
       </c>
       <c r="D675" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="5" t="s">
-        <v>648</v>
+        <v>674</v>
       </c>
       <c r="B676" s="6">
-        <v>960.0</v>
+        <v>1200.0</v>
       </c>
       <c r="C676" s="6">
-        <v>780.0</v>
+        <v>1100.0</v>
       </c>
       <c r="D676" s="7">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="5" t="s">
-        <v>649</v>
+        <v>675</v>
       </c>
       <c r="B677" s="6">
-        <v>526.8</v>
+        <v>175.4</v>
       </c>
       <c r="C677" s="6">
-        <v>449.2</v>
+        <v>166.2</v>
       </c>
       <c r="D677" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="5" t="s">
-        <v>650</v>
+        <v>676</v>
       </c>
       <c r="B678" s="6">
-        <v>528.0</v>
+        <v>343.4</v>
       </c>
       <c r="C678" s="6">
-        <v>495.0</v>
+        <v>315.5</v>
       </c>
       <c r="D678" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="5" t="s">
-        <v>651</v>
+        <v>677</v>
       </c>
       <c r="B679" s="6">
-        <v>635.2</v>
+        <v>355.2</v>
       </c>
       <c r="C679" s="6">
-        <v>598.3</v>
+        <v>326.4</v>
       </c>
       <c r="D679" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="5" t="s">
-        <v>652</v>
+        <v>678</v>
       </c>
       <c r="B680" s="6">
-        <v>240.0</v>
+        <v>419.6</v>
       </c>
       <c r="C680" s="6">
-        <v>225.0</v>
+        <v>385.6</v>
       </c>
       <c r="D680" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="5" t="s">
-        <v>653</v>
+        <v>679</v>
       </c>
       <c r="B681" s="6">
-        <v>263.5</v>
+        <v>657.7</v>
       </c>
       <c r="C681" s="6">
-        <v>238.0</v>
+        <v>605.8</v>
       </c>
       <c r="D681" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="5" t="s">
-        <v>654</v>
+        <v>680</v>
       </c>
       <c r="B682" s="6">
-        <v>304.0</v>
+        <v>592.0</v>
       </c>
       <c r="C682" s="6">
-        <v>275.5</v>
+        <v>544.0</v>
       </c>
       <c r="D682" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="5" t="s">
-        <v>655</v>
+        <v>681</v>
       </c>
       <c r="B683" s="6">
-        <v>374.0</v>
+        <v>1184.0</v>
       </c>
       <c r="C683" s="6">
-        <v>319.1</v>
+        <v>1088.0</v>
       </c>
       <c r="D683" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="5" t="s">
-        <v>656</v>
+        <v>682</v>
       </c>
       <c r="B684" s="6">
-        <v>400.0</v>
+        <v>2220.0</v>
       </c>
       <c r="C684" s="6">
-        <v>362.6</v>
+        <v>2040.0</v>
       </c>
       <c r="D684" s="7">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="5" t="s">
-        <v>657</v>
+        <v>683</v>
       </c>
       <c r="B685" s="6">
-        <v>480.0</v>
+        <v>461.5</v>
       </c>
       <c r="C685" s="6">
-        <v>450.0</v>
+        <v>430.7</v>
       </c>
       <c r="D685" s="7">
         <v>10.0</v>
@@ -12388,77 +12433,83 @@
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="5" t="s">
-        <v>658</v>
+        <v>684</v>
       </c>
       <c r="B686" s="6">
-        <v>6170.9</v>
-      </c>
-      <c r="C686" s="6"/>
+        <v>262.5</v>
+      </c>
+      <c r="C686" s="6">
+        <v>262.5</v>
+      </c>
       <c r="D686" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="5" t="s">
-        <v>659</v>
+        <v>685</v>
       </c>
       <c r="B687" s="6">
-        <v>240.0</v>
-      </c>
-      <c r="C687" s="6"/>
+        <v>936.0</v>
+      </c>
+      <c r="C687" s="6">
+        <v>873.6</v>
+      </c>
       <c r="D687" s="7">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="5" t="s">
-        <v>660</v>
+        <v>686</v>
       </c>
       <c r="B688" s="6">
-        <v>370.0</v>
-      </c>
-      <c r="C688" s="6"/>
+        <v>1540.5</v>
+      </c>
+      <c r="C688" s="6">
+        <v>1386.5</v>
+      </c>
       <c r="D688" s="7">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="5" t="s">
-        <v>661</v>
+        <v>687</v>
       </c>
       <c r="B689" s="6">
-        <v>300.0</v>
+        <v>75.5</v>
       </c>
       <c r="C689" s="6">
-        <v>300.0</v>
+        <v>66.1</v>
       </c>
       <c r="D689" s="7">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="5" t="s">
-        <v>662</v>
+        <v>688</v>
       </c>
       <c r="B690" s="6">
-        <v>120.0</v>
+        <v>15.6</v>
       </c>
       <c r="C690" s="6">
-        <v>105.0</v>
+        <v>15.0</v>
       </c>
       <c r="D690" s="7">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="5" t="s">
-        <v>663</v>
+        <v>689</v>
       </c>
       <c r="B691" s="6">
-        <v>144.0</v>
+        <v>29.7</v>
       </c>
       <c r="C691" s="6">
-        <v>134.5</v>
+        <v>28.2</v>
       </c>
       <c r="D691" s="7">
         <v>50.0</v>
@@ -12466,265 +12517,265 @@
     </row>
     <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="5" t="s">
-        <v>664</v>
+        <v>690</v>
       </c>
       <c r="B692" s="6">
-        <v>105.0</v>
+        <v>224.4</v>
       </c>
       <c r="C692" s="6">
-        <v>98.0</v>
+        <v>194.5</v>
       </c>
       <c r="D692" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="5" t="s">
-        <v>665</v>
+        <v>691</v>
       </c>
       <c r="B693" s="6">
-        <v>16.1</v>
+        <v>570.0</v>
       </c>
       <c r="C693" s="6">
-        <v>14.1</v>
+        <v>570.0</v>
       </c>
       <c r="D693" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="5" t="s">
-        <v>666</v>
+        <v>692</v>
       </c>
       <c r="B694" s="6">
-        <v>1838.0</v>
+        <v>501.3</v>
       </c>
       <c r="C694" s="6">
-        <v>1671.1</v>
+        <v>501.3</v>
       </c>
       <c r="D694" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="5" t="s">
-        <v>667</v>
+        <v>693</v>
       </c>
       <c r="B695" s="6">
-        <v>3517.7</v>
+        <v>2501.7</v>
       </c>
       <c r="C695" s="6">
-        <v>3220.3</v>
+        <v>2465.8</v>
       </c>
       <c r="D695" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="5" t="s">
-        <v>668</v>
+        <v>694</v>
       </c>
       <c r="B696" s="6">
-        <v>475.7</v>
+        <v>2179.9</v>
       </c>
       <c r="C696" s="6">
-        <v>441.7</v>
+        <v>2027.6</v>
       </c>
       <c r="D696" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="5" t="s">
-        <v>669</v>
+        <v>695</v>
       </c>
       <c r="B697" s="6">
-        <v>900.0</v>
+        <v>197.0</v>
       </c>
       <c r="C697" s="6">
-        <v>800.0</v>
+        <v>186.7</v>
       </c>
       <c r="D697" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="5" t="s">
-        <v>670</v>
+        <v>696</v>
       </c>
       <c r="B698" s="6">
-        <v>750.0</v>
+        <v>200.0</v>
       </c>
       <c r="C698" s="6">
-        <v>680.0</v>
+        <v>190.0</v>
       </c>
       <c r="D698" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="5" t="s">
-        <v>671</v>
+        <v>697</v>
       </c>
       <c r="B699" s="6">
-        <v>281.2</v>
+        <v>252.8</v>
       </c>
       <c r="C699" s="6">
-        <v>258.4</v>
+        <v>240.7</v>
       </c>
       <c r="D699" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="5" t="s">
-        <v>672</v>
+        <v>698</v>
       </c>
       <c r="B700" s="6">
-        <v>518.0</v>
+        <v>230.0</v>
       </c>
       <c r="C700" s="6">
-        <v>476.0</v>
+        <v>220.0</v>
       </c>
       <c r="D700" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="5" t="s">
-        <v>673</v>
+        <v>699</v>
       </c>
       <c r="B701" s="6">
-        <v>560.0</v>
+        <v>175.0</v>
       </c>
       <c r="C701" s="6">
-        <v>520.0</v>
+        <v>165.0</v>
       </c>
       <c r="D701" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="5" t="s">
-        <v>674</v>
+        <v>700</v>
       </c>
       <c r="B702" s="6">
-        <v>1476.9</v>
+        <v>160.0</v>
       </c>
       <c r="C702" s="6">
-        <v>1357.2</v>
+        <v>150.0</v>
       </c>
       <c r="D702" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="5" t="s">
-        <v>675</v>
+        <v>701</v>
       </c>
       <c r="B703" s="6">
-        <v>2368.0</v>
+        <v>450.0</v>
       </c>
       <c r="C703" s="6">
-        <v>2176.0</v>
+        <v>403.0</v>
       </c>
       <c r="D703" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="5" t="s">
-        <v>676</v>
+        <v>702</v>
       </c>
       <c r="B704" s="6">
-        <v>1200.0</v>
+        <v>260.0</v>
       </c>
       <c r="C704" s="6">
-        <v>1100.0</v>
+        <v>250.0</v>
       </c>
       <c r="D704" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="5" t="s">
-        <v>677</v>
+        <v>703</v>
       </c>
       <c r="B705" s="6">
-        <v>175.4</v>
+        <v>550.0</v>
       </c>
       <c r="C705" s="6">
-        <v>166.2</v>
+        <v>480.6</v>
       </c>
       <c r="D705" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="5" t="s">
-        <v>678</v>
+        <v>704</v>
       </c>
       <c r="B706" s="6">
-        <v>343.4</v>
+        <v>800.0</v>
       </c>
       <c r="C706" s="6">
-        <v>315.5</v>
+        <v>650.0</v>
       </c>
       <c r="D706" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="5" t="s">
-        <v>679</v>
+        <v>705</v>
       </c>
       <c r="B707" s="6">
-        <v>355.2</v>
+        <v>340.0</v>
       </c>
       <c r="C707" s="6">
-        <v>326.4</v>
+        <v>310.5</v>
       </c>
       <c r="D707" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="5" t="s">
-        <v>680</v>
+        <v>706</v>
       </c>
       <c r="B708" s="6">
-        <v>419.6</v>
+        <v>66.1</v>
       </c>
       <c r="C708" s="6">
-        <v>385.6</v>
+        <v>56.6</v>
       </c>
       <c r="D708" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="5" t="s">
-        <v>681</v>
+        <v>707</v>
       </c>
       <c r="B709" s="6">
-        <v>657.7</v>
+        <v>94.5</v>
       </c>
       <c r="C709" s="6">
-        <v>605.8</v>
+        <v>91.0</v>
       </c>
       <c r="D709" s="7">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="5" t="s">
-        <v>682</v>
+        <v>708</v>
       </c>
       <c r="B710" s="6">
-        <v>592.0</v>
+        <v>4224.7</v>
       </c>
       <c r="C710" s="6">
-        <v>544.0</v>
+        <v>4062.7</v>
       </c>
       <c r="D710" s="7">
         <v>5.0</v>
@@ -12732,27 +12783,27 @@
     </row>
     <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="5" t="s">
-        <v>683</v>
+        <v>709</v>
       </c>
       <c r="B711" s="6">
-        <v>1184.0</v>
+        <v>829.4</v>
       </c>
       <c r="C711" s="6">
-        <v>1088.0</v>
+        <v>0.0</v>
       </c>
       <c r="D711" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="5" t="s">
-        <v>684</v>
+        <v>710</v>
       </c>
       <c r="B712" s="6">
-        <v>2220.0</v>
+        <v>2500.0</v>
       </c>
       <c r="C712" s="6">
-        <v>2040.0</v>
+        <v>1500.0</v>
       </c>
       <c r="D712" s="7">
         <v>5.0</v>
@@ -12760,27 +12811,27 @@
     </row>
     <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="5" t="s">
-        <v>685</v>
+        <v>711</v>
       </c>
       <c r="B713" s="6">
-        <v>461.5</v>
+        <v>2530.0</v>
       </c>
       <c r="C713" s="6">
-        <v>430.7</v>
+        <v>1420.7</v>
       </c>
       <c r="D713" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="5" t="s">
-        <v>686</v>
+        <v>712</v>
       </c>
       <c r="B714" s="6">
-        <v>262.5</v>
+        <v>1527.8</v>
       </c>
       <c r="C714" s="6">
-        <v>262.5</v>
+        <v>1527.8</v>
       </c>
       <c r="D714" s="7">
         <v>3.0</v>
@@ -12788,346 +12839,342 @@
     </row>
     <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="5" t="s">
-        <v>687</v>
+        <v>713</v>
       </c>
       <c r="B715" s="6">
-        <v>936.0</v>
+        <v>504.0</v>
       </c>
       <c r="C715" s="6">
-        <v>873.6</v>
+        <v>504.0</v>
       </c>
       <c r="D715" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="5" t="s">
-        <v>688</v>
+        <v>714</v>
       </c>
       <c r="B716" s="6">
-        <v>1540.5</v>
+        <v>800.0</v>
       </c>
       <c r="C716" s="6">
-        <v>1386.5</v>
+        <v>800.0</v>
       </c>
       <c r="D716" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="5" t="s">
-        <v>689</v>
+        <v>715</v>
       </c>
       <c r="B717" s="6">
-        <v>75.5</v>
+        <v>1399.8</v>
       </c>
       <c r="C717" s="6">
-        <v>66.1</v>
+        <v>1399.8</v>
       </c>
       <c r="D717" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="5" t="s">
-        <v>690</v>
+        <v>716</v>
       </c>
       <c r="B718" s="6">
-        <v>15.6</v>
+        <v>2539.7</v>
       </c>
       <c r="C718" s="6">
-        <v>15.0</v>
+        <v>2222.2</v>
       </c>
       <c r="D718" s="7">
-        <v>100.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="5" t="s">
-        <v>691</v>
+        <v>717</v>
       </c>
       <c r="B719" s="6">
-        <v>29.7</v>
+        <v>5000.0</v>
       </c>
       <c r="C719" s="6">
-        <v>28.2</v>
+        <v>5000.0</v>
       </c>
       <c r="D719" s="7">
-        <v>50.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="5" t="s">
-        <v>692</v>
+        <v>718</v>
       </c>
       <c r="B720" s="6">
-        <v>224.4</v>
+        <v>11040.0</v>
       </c>
       <c r="C720" s="6">
-        <v>194.5</v>
+        <v>10560.0</v>
       </c>
       <c r="D720" s="7">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="5" t="s">
-        <v>693</v>
+        <v>719</v>
       </c>
       <c r="B721" s="6">
-        <v>570.0</v>
+        <v>1000.0</v>
       </c>
       <c r="C721" s="6">
-        <v>570.0</v>
+        <v>900.0</v>
       </c>
       <c r="D721" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="5" t="s">
-        <v>694</v>
+        <v>720</v>
       </c>
       <c r="B722" s="6">
-        <v>501.3</v>
+        <v>226.5</v>
       </c>
       <c r="C722" s="6">
-        <v>501.3</v>
+        <v>0.0</v>
       </c>
       <c r="D722" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="5" t="s">
-        <v>695</v>
+        <v>721</v>
       </c>
       <c r="B723" s="6">
-        <v>2501.7</v>
-      </c>
-      <c r="C723" s="6">
-        <v>2465.8</v>
-      </c>
+        <v>1500.0</v>
+      </c>
+      <c r="C723" s="6"/>
       <c r="D723" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="5" t="s">
-        <v>696</v>
+        <v>722</v>
       </c>
       <c r="B724" s="6">
-        <v>2179.9</v>
+        <v>3396.6</v>
       </c>
       <c r="C724" s="6">
-        <v>2027.6</v>
+        <v>3229.2</v>
       </c>
       <c r="D724" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="5" t="s">
-        <v>697</v>
+        <v>723</v>
       </c>
       <c r="B725" s="6">
-        <v>197.0</v>
+        <v>6900.0</v>
       </c>
       <c r="C725" s="6">
-        <v>186.7</v>
+        <v>6600.0</v>
       </c>
       <c r="D725" s="7">
-        <v>50.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="5" t="s">
-        <v>698</v>
+        <v>724</v>
       </c>
       <c r="B726" s="6">
-        <v>200.0</v>
+        <v>1704.0</v>
       </c>
       <c r="C726" s="6">
-        <v>190.0</v>
+        <v>0.0</v>
       </c>
       <c r="D726" s="7">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="5" t="s">
-        <v>699</v>
+        <v>725</v>
       </c>
       <c r="B727" s="6">
-        <v>252.8</v>
+        <v>1200.0</v>
       </c>
       <c r="C727" s="6">
-        <v>240.7</v>
+        <v>1000.0</v>
       </c>
       <c r="D727" s="7">
-        <v>50.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="5" t="s">
-        <v>700</v>
+        <v>726</v>
       </c>
       <c r="B728" s="6">
-        <v>230.0</v>
+        <v>840.0</v>
       </c>
       <c r="C728" s="6">
-        <v>220.0</v>
+        <v>780.0</v>
       </c>
       <c r="D728" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="5" t="s">
-        <v>701</v>
+        <v>727</v>
       </c>
       <c r="B729" s="6">
-        <v>175.0</v>
+        <v>980.0</v>
       </c>
       <c r="C729" s="6">
-        <v>165.0</v>
+        <v>910.0</v>
       </c>
       <c r="D729" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="5" t="s">
-        <v>702</v>
+        <v>728</v>
       </c>
       <c r="B730" s="6">
-        <v>160.0</v>
+        <v>1040.0</v>
       </c>
       <c r="C730" s="6">
-        <v>150.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D730" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="5" t="s">
-        <v>703</v>
+        <v>729</v>
       </c>
       <c r="B731" s="6">
-        <v>450.0</v>
+        <v>1495.0</v>
       </c>
       <c r="C731" s="6">
-        <v>403.0</v>
+        <v>1437.5</v>
       </c>
       <c r="D731" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="5" t="s">
-        <v>704</v>
+        <v>730</v>
       </c>
       <c r="B732" s="6">
-        <v>260.0</v>
+        <v>2826.6</v>
       </c>
       <c r="C732" s="6">
-        <v>250.0</v>
+        <v>2782.1</v>
       </c>
       <c r="D732" s="7">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="5" t="s">
-        <v>705</v>
+        <v>731</v>
       </c>
       <c r="B733" s="6">
-        <v>550.0</v>
+        <v>120.0</v>
       </c>
       <c r="C733" s="6">
-        <v>480.6</v>
+        <v>120.0</v>
       </c>
       <c r="D733" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="5" t="s">
-        <v>706</v>
+        <v>732</v>
       </c>
       <c r="B734" s="6">
-        <v>800.0</v>
+        <v>30.0</v>
       </c>
       <c r="C734" s="6">
-        <v>650.0</v>
+        <v>30.0</v>
       </c>
       <c r="D734" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="5" t="s">
-        <v>707</v>
+        <v>733</v>
       </c>
       <c r="B735" s="6">
-        <v>340.0</v>
+        <v>899.0</v>
       </c>
       <c r="C735" s="6">
-        <v>310.5</v>
+        <v>899.0</v>
       </c>
       <c r="D735" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="5" t="s">
-        <v>708</v>
+        <v>734</v>
       </c>
       <c r="B736" s="6">
-        <v>66.1</v>
+        <v>288.0</v>
       </c>
       <c r="C736" s="6">
-        <v>56.6</v>
+        <v>288.0</v>
       </c>
       <c r="D736" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="5" t="s">
-        <v>709</v>
+        <v>735</v>
       </c>
       <c r="B737" s="6">
-        <v>94.5</v>
-      </c>
-      <c r="C737" s="6">
-        <v>91.0</v>
-      </c>
+        <v>-517.4</v>
+      </c>
+      <c r="C737" s="6"/>
       <c r="D737" s="7">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="5" t="s">
-        <v>710</v>
+        <v>736</v>
       </c>
       <c r="B738" s="6">
-        <v>4224.7</v>
+        <v>266.1</v>
       </c>
       <c r="C738" s="6">
-        <v>4062.7</v>
+        <v>245.6</v>
       </c>
       <c r="D738" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="5" t="s">
-        <v>711</v>
+        <v>737</v>
       </c>
       <c r="B739" s="6">
-        <v>829.4</v>
+        <v>190.7</v>
       </c>
       <c r="C739" s="6">
         <v>0.0</v>
@@ -13138,41 +13185,41 @@
     </row>
     <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="5" t="s">
-        <v>712</v>
+        <v>738</v>
       </c>
       <c r="B740" s="6">
-        <v>2500.0</v>
+        <v>2492.0</v>
       </c>
       <c r="C740" s="6">
-        <v>1500.0</v>
+        <v>2314.0</v>
       </c>
       <c r="D740" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="5" t="s">
-        <v>713</v>
+        <v>739</v>
       </c>
       <c r="B741" s="6">
-        <v>2530.0</v>
+        <v>6539.4</v>
       </c>
       <c r="C741" s="6">
-        <v>1420.7</v>
+        <v>6277.9</v>
       </c>
       <c r="D741" s="7">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="5" t="s">
-        <v>714</v>
+        <v>740</v>
       </c>
       <c r="B742" s="6">
-        <v>1527.8</v>
+        <v>17614.8</v>
       </c>
       <c r="C742" s="6">
-        <v>1527.8</v>
+        <v>16853.8</v>
       </c>
       <c r="D742" s="7">
         <v>3.0</v>
@@ -13180,13 +13227,13 @@
     </row>
     <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="5" t="s">
-        <v>715</v>
+        <v>741</v>
       </c>
       <c r="B743" s="6">
-        <v>504.0</v>
+        <v>591.5</v>
       </c>
       <c r="C743" s="6">
-        <v>504.0</v>
+        <v>537.7</v>
       </c>
       <c r="D743" s="7">
         <v>3.0</v>
@@ -13194,27 +13241,27 @@
     </row>
     <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="5" t="s">
-        <v>716</v>
+        <v>742</v>
       </c>
       <c r="B744" s="6">
-        <v>800.0</v>
+        <v>3755.4</v>
       </c>
       <c r="C744" s="6">
-        <v>800.0</v>
+        <v>3755.4</v>
       </c>
       <c r="D744" s="7">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="5" t="s">
-        <v>717</v>
+        <v>743</v>
       </c>
       <c r="B745" s="6">
-        <v>1399.8</v>
+        <v>3700.0</v>
       </c>
       <c r="C745" s="6">
-        <v>1399.8</v>
+        <v>3700.0</v>
       </c>
       <c r="D745" s="7">
         <v>3.0</v>
@@ -13222,123 +13269,125 @@
     </row>
     <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="5" t="s">
-        <v>718</v>
+        <v>744</v>
       </c>
       <c r="B746" s="6">
-        <v>2539.7</v>
+        <v>368.4</v>
       </c>
       <c r="C746" s="6">
-        <v>2222.2</v>
+        <v>327.4</v>
       </c>
       <c r="D746" s="7">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="5" t="s">
-        <v>719</v>
+        <v>745</v>
       </c>
       <c r="B747" s="6">
-        <v>5000.0</v>
+        <v>900.0</v>
       </c>
       <c r="C747" s="6">
-        <v>5000.0</v>
+        <v>900.0</v>
       </c>
       <c r="D747" s="7">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="5" t="s">
-        <v>720</v>
+        <v>746</v>
       </c>
       <c r="B748" s="6">
-        <v>11040.0</v>
+        <v>160.8</v>
       </c>
       <c r="C748" s="6">
-        <v>10560.0</v>
+        <v>154.6</v>
       </c>
       <c r="D748" s="7">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="5" t="s">
-        <v>721</v>
+        <v>747</v>
       </c>
       <c r="B749" s="6">
-        <v>1000.0</v>
+        <v>2380.0</v>
       </c>
       <c r="C749" s="6">
-        <v>900.0</v>
+        <v>2380.0</v>
       </c>
       <c r="D749" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="5" t="s">
-        <v>722</v>
+        <v>748</v>
       </c>
       <c r="B750" s="6">
-        <v>226.5</v>
+        <v>910.0</v>
       </c>
       <c r="C750" s="6">
-        <v>0.0</v>
+        <v>910.0</v>
       </c>
       <c r="D750" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="5" t="s">
-        <v>723</v>
+        <v>749</v>
       </c>
       <c r="B751" s="6">
-        <v>1500.0</v>
-      </c>
-      <c r="C751" s="6"/>
+        <v>38.0</v>
+      </c>
+      <c r="C751" s="6">
+        <v>34.2</v>
+      </c>
       <c r="D751" s="7">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="5" t="s">
-        <v>724</v>
+        <v>750</v>
       </c>
       <c r="B752" s="6">
-        <v>3396.6</v>
+        <v>40.6</v>
       </c>
       <c r="C752" s="6">
-        <v>3229.2</v>
+        <v>37.7</v>
       </c>
       <c r="D752" s="7">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="5" t="s">
-        <v>725</v>
+        <v>751</v>
       </c>
       <c r="B753" s="6">
-        <v>6900.0</v>
+        <v>59.2</v>
       </c>
       <c r="C753" s="6">
-        <v>6600.0</v>
+        <v>52.6</v>
       </c>
       <c r="D753" s="7">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="5" t="s">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="B754" s="6">
-        <v>1704.0</v>
+        <v>66.7</v>
       </c>
       <c r="C754" s="6">
-        <v>0.0</v>
+        <v>66.7</v>
       </c>
       <c r="D754" s="7">
         <v>0.0</v>
@@ -13346,55 +13395,55 @@
     </row>
     <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="5" t="s">
-        <v>727</v>
+        <v>753</v>
       </c>
       <c r="B755" s="6">
-        <v>1200.0</v>
+        <v>152.1</v>
       </c>
       <c r="C755" s="6">
-        <v>1000.0</v>
+        <v>133.9</v>
       </c>
       <c r="D755" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="5" t="s">
-        <v>728</v>
+        <v>754</v>
       </c>
       <c r="B756" s="6">
-        <v>840.0</v>
+        <v>37.8</v>
       </c>
       <c r="C756" s="6">
-        <v>780.0</v>
+        <v>18.9</v>
       </c>
       <c r="D756" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="757" ht="15.75" customHeight="1">
       <c r="A757" s="5" t="s">
-        <v>729</v>
+        <v>755</v>
       </c>
       <c r="B757" s="6">
-        <v>980.0</v>
+        <v>436.8</v>
       </c>
       <c r="C757" s="6">
-        <v>910.0</v>
+        <v>436.8</v>
       </c>
       <c r="D757" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="5" t="s">
-        <v>730</v>
+        <v>756</v>
       </c>
       <c r="B758" s="6">
-        <v>1040.0</v>
+        <v>966.0</v>
       </c>
       <c r="C758" s="6">
-        <v>1000.0</v>
+        <v>910.0</v>
       </c>
       <c r="D758" s="7">
         <v>5.0</v>
@@ -13402,137 +13451,139 @@
     </row>
     <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="5" t="s">
-        <v>731</v>
+        <v>757</v>
       </c>
       <c r="B759" s="6">
-        <v>1495.0</v>
+        <v>1388.4</v>
       </c>
       <c r="C759" s="6">
-        <v>1437.5</v>
+        <v>1315.5</v>
       </c>
       <c r="D759" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="5" t="s">
-        <v>732</v>
+        <v>758</v>
       </c>
       <c r="B760" s="6">
-        <v>2826.6</v>
+        <v>1144.0</v>
       </c>
       <c r="C760" s="6">
-        <v>2782.1</v>
+        <v>1068.6</v>
       </c>
       <c r="D760" s="7">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="5" t="s">
-        <v>733</v>
+        <v>759</v>
       </c>
       <c r="B761" s="6">
-        <v>120.0</v>
+        <v>33.2</v>
       </c>
       <c r="C761" s="6">
-        <v>120.0</v>
+        <v>26.6</v>
       </c>
       <c r="D761" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="5" t="s">
-        <v>734</v>
+        <v>760</v>
       </c>
       <c r="B762" s="6">
-        <v>30.0</v>
+        <v>100.0</v>
       </c>
       <c r="C762" s="6">
-        <v>30.0</v>
+        <v>90.0</v>
       </c>
       <c r="D762" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="5" t="s">
-        <v>735</v>
+        <v>761</v>
       </c>
       <c r="B763" s="6">
-        <v>899.0</v>
+        <v>150.0</v>
       </c>
       <c r="C763" s="6">
-        <v>899.0</v>
+        <v>140.0</v>
       </c>
       <c r="D763" s="7">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="5" t="s">
-        <v>736</v>
+        <v>762</v>
       </c>
       <c r="B764" s="6">
-        <v>288.0</v>
+        <v>65.0</v>
       </c>
       <c r="C764" s="6">
-        <v>288.0</v>
+        <v>60.0</v>
       </c>
       <c r="D764" s="7">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="5" t="s">
-        <v>737</v>
+        <v>763</v>
       </c>
       <c r="B765" s="6">
-        <v>-517.4</v>
-      </c>
-      <c r="C765" s="6"/>
+        <v>1204.0</v>
+      </c>
+      <c r="C765" s="6">
+        <v>1204.0</v>
+      </c>
       <c r="D765" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="5" t="s">
-        <v>738</v>
+        <v>764</v>
       </c>
       <c r="B766" s="6">
-        <v>266.1</v>
+        <v>759.2</v>
       </c>
       <c r="C766" s="6">
-        <v>245.6</v>
+        <v>740.3</v>
       </c>
       <c r="D766" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="5" t="s">
-        <v>739</v>
+        <v>765</v>
       </c>
       <c r="B767" s="6">
-        <v>190.7</v>
+        <v>4851.0</v>
       </c>
       <c r="C767" s="6">
-        <v>0.0</v>
+        <v>4527.6</v>
       </c>
       <c r="D767" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="5" t="s">
-        <v>740</v>
+        <v>766</v>
       </c>
       <c r="B768" s="6">
-        <v>2492.0</v>
+        <v>49.4</v>
       </c>
       <c r="C768" s="6">
-        <v>2314.0</v>
+        <v>47.5</v>
       </c>
       <c r="D768" s="7">
         <v>10.0</v>
@@ -13540,13 +13591,13 @@
     </row>
     <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="5" t="s">
-        <v>741</v>
+        <v>767</v>
       </c>
       <c r="B769" s="6">
-        <v>6539.4</v>
+        <v>46.8</v>
       </c>
       <c r="C769" s="6">
-        <v>6277.9</v>
+        <v>45.0</v>
       </c>
       <c r="D769" s="7">
         <v>25.0</v>
@@ -13554,69 +13605,69 @@
     </row>
     <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="5" t="s">
-        <v>742</v>
+        <v>768</v>
       </c>
       <c r="B770" s="6">
-        <v>17614.8</v>
+        <v>53.3</v>
       </c>
       <c r="C770" s="6">
-        <v>16853.8</v>
+        <v>51.2</v>
       </c>
       <c r="D770" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="5" t="s">
-        <v>743</v>
+        <v>769</v>
       </c>
       <c r="B771" s="6">
-        <v>591.5</v>
+        <v>54.0</v>
       </c>
       <c r="C771" s="6">
-        <v>537.7</v>
+        <v>52.0</v>
       </c>
       <c r="D771" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="5" t="s">
-        <v>744</v>
+        <v>770</v>
       </c>
       <c r="B772" s="6">
-        <v>3755.4</v>
+        <v>60.9</v>
       </c>
       <c r="C772" s="6">
-        <v>3755.4</v>
+        <v>56.7</v>
       </c>
       <c r="D772" s="7">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="5" t="s">
-        <v>745</v>
+        <v>771</v>
       </c>
       <c r="B773" s="6">
-        <v>3700.0</v>
+        <v>62.4</v>
       </c>
       <c r="C773" s="6">
-        <v>3700.0</v>
+        <v>60.0</v>
       </c>
       <c r="D773" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="5" t="s">
-        <v>746</v>
+        <v>772</v>
       </c>
       <c r="B774" s="6">
-        <v>368.4</v>
+        <v>700.0</v>
       </c>
       <c r="C774" s="6">
-        <v>327.4</v>
+        <v>580.0</v>
       </c>
       <c r="D774" s="7">
         <v>3.0</v>
@@ -13624,27 +13675,27 @@
     </row>
     <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="5" t="s">
-        <v>747</v>
+        <v>773</v>
       </c>
       <c r="B775" s="6">
-        <v>900.0</v>
+        <v>1000.0</v>
       </c>
       <c r="C775" s="6">
-        <v>900.0</v>
+        <v>960.0</v>
       </c>
       <c r="D775" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="5" t="s">
-        <v>748</v>
+        <v>774</v>
       </c>
       <c r="B776" s="6">
-        <v>160.8</v>
+        <v>1187.5</v>
       </c>
       <c r="C776" s="6">
-        <v>154.6</v>
+        <v>1140.0</v>
       </c>
       <c r="D776" s="7">
         <v>5.0</v>
@@ -13652,209 +13703,209 @@
     </row>
     <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="5" t="s">
-        <v>749</v>
+        <v>775</v>
       </c>
       <c r="B777" s="6">
-        <v>2380.0</v>
+        <v>1682.3</v>
       </c>
       <c r="C777" s="6">
-        <v>2380.0</v>
+        <v>1570.1</v>
       </c>
       <c r="D777" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="5" t="s">
-        <v>750</v>
+        <v>776</v>
       </c>
       <c r="B778" s="6">
-        <v>910.0</v>
+        <v>1459.7</v>
       </c>
       <c r="C778" s="6">
-        <v>910.0</v>
+        <v>1357.3</v>
       </c>
       <c r="D778" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="5" t="s">
-        <v>751</v>
+        <v>777</v>
       </c>
       <c r="B779" s="6">
-        <v>38.0</v>
+        <v>1885.1</v>
       </c>
       <c r="C779" s="6">
-        <v>34.2</v>
+        <v>1803.1</v>
       </c>
       <c r="D779" s="7">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="5" t="s">
-        <v>752</v>
+        <v>778</v>
       </c>
       <c r="B780" s="6">
-        <v>40.6</v>
+        <v>1821.6</v>
       </c>
       <c r="C780" s="6">
-        <v>37.7</v>
+        <v>1742.4</v>
       </c>
       <c r="D780" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="5" t="s">
-        <v>753</v>
+        <v>779</v>
       </c>
       <c r="B781" s="6">
-        <v>59.2</v>
+        <v>361.2</v>
       </c>
       <c r="C781" s="6">
-        <v>52.6</v>
+        <v>335.4</v>
       </c>
       <c r="D781" s="7">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="5" t="s">
-        <v>754</v>
+        <v>780</v>
       </c>
       <c r="B782" s="6">
-        <v>66.7</v>
+        <v>1200.0</v>
       </c>
       <c r="C782" s="6">
-        <v>66.7</v>
+        <v>1200.0</v>
       </c>
       <c r="D782" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="5" t="s">
-        <v>755</v>
+        <v>781</v>
       </c>
       <c r="B783" s="6">
-        <v>152.1</v>
+        <v>3621.8</v>
       </c>
       <c r="C783" s="6">
-        <v>133.9</v>
+        <v>3621.8</v>
       </c>
       <c r="D783" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="5" t="s">
-        <v>756</v>
+        <v>782</v>
       </c>
       <c r="B784" s="6">
-        <v>37.8</v>
+        <v>646.8</v>
       </c>
       <c r="C784" s="6">
-        <v>18.9</v>
+        <v>600.6</v>
       </c>
       <c r="D784" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="5" t="s">
-        <v>757</v>
+        <v>783</v>
       </c>
       <c r="B785" s="6">
-        <v>436.8</v>
+        <v>281.8</v>
       </c>
       <c r="C785" s="6">
-        <v>436.8</v>
+        <v>263.0</v>
       </c>
       <c r="D785" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="5" t="s">
-        <v>758</v>
+        <v>784</v>
       </c>
       <c r="B786" s="6">
-        <v>966.0</v>
+        <v>281.5</v>
       </c>
       <c r="C786" s="6">
-        <v>910.0</v>
+        <v>241.2</v>
       </c>
       <c r="D786" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="5" t="s">
-        <v>759</v>
+        <v>785</v>
       </c>
       <c r="B787" s="6">
-        <v>1388.4</v>
+        <v>786.6</v>
       </c>
       <c r="C787" s="6">
-        <v>1315.5</v>
+        <v>757.5</v>
       </c>
       <c r="D787" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="5" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="B788" s="6">
-        <v>1144.0</v>
+        <v>180.0</v>
       </c>
       <c r="C788" s="6">
-        <v>1068.6</v>
+        <v>162.0</v>
       </c>
       <c r="D788" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="5" t="s">
-        <v>761</v>
+        <v>787</v>
       </c>
       <c r="B789" s="6">
-        <v>33.2</v>
+        <v>1071.4</v>
       </c>
       <c r="C789" s="6">
-        <v>26.6</v>
+        <v>1011.9</v>
       </c>
       <c r="D789" s="7">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="5" t="s">
-        <v>762</v>
+        <v>788</v>
       </c>
       <c r="B790" s="6">
-        <v>100.0</v>
+        <v>680.0</v>
       </c>
       <c r="C790" s="6">
-        <v>90.0</v>
+        <v>660.0</v>
       </c>
       <c r="D790" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="5" t="s">
-        <v>763</v>
+        <v>789</v>
       </c>
       <c r="B791" s="6">
-        <v>150.0</v>
+        <v>3200.0</v>
       </c>
       <c r="C791" s="6">
-        <v>140.0</v>
+        <v>3200.0</v>
       </c>
       <c r="D791" s="7">
         <v>50.0</v>
@@ -13862,27 +13913,27 @@
     </row>
     <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="5" t="s">
-        <v>764</v>
+        <v>790</v>
       </c>
       <c r="B792" s="6">
-        <v>65.0</v>
+        <v>100.0</v>
       </c>
       <c r="C792" s="6">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="D792" s="7">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="5" t="s">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="B793" s="6">
-        <v>1204.0</v>
+        <v>1485.0</v>
       </c>
       <c r="C793" s="6">
-        <v>1204.0</v>
+        <v>1375.0</v>
       </c>
       <c r="D793" s="7">
         <v>5.0</v>
@@ -13890,181 +13941,179 @@
     </row>
     <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="5" t="s">
-        <v>766</v>
+        <v>792</v>
       </c>
       <c r="B794" s="6">
-        <v>759.2</v>
+        <v>781.5</v>
       </c>
       <c r="C794" s="6">
-        <v>740.3</v>
+        <v>721.4</v>
       </c>
       <c r="D794" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="5" t="s">
-        <v>767</v>
+        <v>793</v>
       </c>
       <c r="B795" s="6">
-        <v>4851.0</v>
+        <v>500.0</v>
       </c>
       <c r="C795" s="6">
-        <v>4527.6</v>
+        <v>500.0</v>
       </c>
       <c r="D795" s="7">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="5" t="s">
-        <v>768</v>
+        <v>794</v>
       </c>
       <c r="B796" s="6">
-        <v>49.4</v>
+        <v>169.0</v>
       </c>
       <c r="C796" s="6">
-        <v>47.5</v>
+        <v>162.5</v>
       </c>
       <c r="D796" s="7">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="5" t="s">
-        <v>769</v>
+        <v>795</v>
       </c>
       <c r="B797" s="6">
-        <v>46.8</v>
+        <v>361.4</v>
       </c>
       <c r="C797" s="6">
-        <v>45.0</v>
+        <v>338.0</v>
       </c>
       <c r="D797" s="7">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="5" t="s">
-        <v>770</v>
+        <v>796</v>
       </c>
       <c r="B798" s="6">
-        <v>53.3</v>
+        <v>3213.3</v>
       </c>
       <c r="C798" s="6">
-        <v>51.2</v>
+        <v>2983.8</v>
       </c>
       <c r="D798" s="7">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="5" t="s">
-        <v>771</v>
+        <v>797</v>
       </c>
       <c r="B799" s="6">
-        <v>54.0</v>
+        <v>3080.0</v>
       </c>
       <c r="C799" s="6">
-        <v>52.0</v>
+        <v>3080.0</v>
       </c>
       <c r="D799" s="7">
-        <v>50.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="5" t="s">
-        <v>772</v>
+        <v>798</v>
       </c>
       <c r="B800" s="6">
-        <v>60.9</v>
+        <v>473.5</v>
       </c>
       <c r="C800" s="6">
-        <v>56.7</v>
+        <v>439.7</v>
       </c>
       <c r="D800" s="7">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="5" t="s">
-        <v>773</v>
+        <v>799</v>
       </c>
       <c r="B801" s="6">
-        <v>62.4</v>
+        <v>184.7</v>
       </c>
       <c r="C801" s="6">
-        <v>60.0</v>
+        <v>155.6</v>
       </c>
       <c r="D801" s="7">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="5" t="s">
-        <v>774</v>
+        <v>800</v>
       </c>
       <c r="B802" s="6">
-        <v>700.0</v>
+        <v>450.0</v>
       </c>
       <c r="C802" s="6">
-        <v>580.0</v>
+        <v>420.0</v>
       </c>
       <c r="D802" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="5" t="s">
-        <v>775</v>
+        <v>801</v>
       </c>
       <c r="B803" s="6">
-        <v>1000.0</v>
+        <v>630.0</v>
       </c>
       <c r="C803" s="6">
-        <v>960.0</v>
+        <v>600.0</v>
       </c>
       <c r="D803" s="7">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="5" t="s">
-        <v>776</v>
+        <v>802</v>
       </c>
       <c r="B804" s="6">
-        <v>1187.5</v>
+        <v>135.2</v>
       </c>
       <c r="C804" s="6">
-        <v>1140.0</v>
+        <v>127.4</v>
       </c>
       <c r="D804" s="7">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="5" t="s">
-        <v>777</v>
+        <v>803</v>
       </c>
       <c r="B805" s="6">
-        <v>1682.3</v>
-      </c>
-      <c r="C805" s="6">
-        <v>1570.1</v>
-      </c>
+        <v>905.4</v>
+      </c>
+      <c r="C805" s="6"/>
       <c r="D805" s="7">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="5" t="s">
-        <v>778</v>
+        <v>804</v>
       </c>
       <c r="B806" s="6">
-        <v>1459.7</v>
+        <v>1500.0</v>
       </c>
       <c r="C806" s="6">
-        <v>1357.3</v>
+        <v>1500.0</v>
       </c>
       <c r="D806" s="7">
         <v>5.0</v>
@@ -14072,27 +14121,27 @@
     </row>
     <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="5" t="s">
-        <v>779</v>
+        <v>805</v>
       </c>
       <c r="B807" s="6">
-        <v>1885.1</v>
+        <v>1600.0</v>
       </c>
       <c r="C807" s="6">
-        <v>1803.1</v>
+        <v>1600.0</v>
       </c>
       <c r="D807" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="5" t="s">
-        <v>780</v>
+        <v>806</v>
       </c>
       <c r="B808" s="6">
-        <v>1821.6</v>
+        <v>325.8</v>
       </c>
       <c r="C808" s="6">
-        <v>1742.4</v>
+        <v>293.2</v>
       </c>
       <c r="D808" s="7">
         <v>3.0</v>
@@ -14100,27 +14149,27 @@
     </row>
     <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="5" t="s">
-        <v>781</v>
+        <v>807</v>
       </c>
       <c r="B809" s="6">
-        <v>361.2</v>
+        <v>1200.0</v>
       </c>
       <c r="C809" s="6">
-        <v>335.4</v>
+        <v>1200.0</v>
       </c>
       <c r="D809" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="5" t="s">
-        <v>782</v>
+        <v>808</v>
       </c>
       <c r="B810" s="6">
-        <v>1200.0</v>
+        <v>617.0</v>
       </c>
       <c r="C810" s="6">
-        <v>1200.0</v>
+        <v>567.6</v>
       </c>
       <c r="D810" s="7">
         <v>3.0</v>
@@ -14128,1423 +14177,1033 @@
     </row>
     <row r="811" ht="15.75" customHeight="1">
       <c r="A811" s="5" t="s">
-        <v>783</v>
+        <v>809</v>
       </c>
       <c r="B811" s="6">
-        <v>3621.8</v>
+        <v>521.3</v>
       </c>
       <c r="C811" s="6">
-        <v>3621.8</v>
+        <v>488.7</v>
       </c>
       <c r="D811" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="5" t="s">
-        <v>784</v>
+        <v>810</v>
       </c>
       <c r="B812" s="6">
-        <v>646.8</v>
+        <v>195.0</v>
       </c>
       <c r="C812" s="6">
-        <v>600.6</v>
+        <v>187.5</v>
       </c>
       <c r="D812" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="5" t="s">
-        <v>785</v>
+        <v>811</v>
       </c>
       <c r="B813" s="6">
-        <v>281.8</v>
+        <v>63.0</v>
       </c>
       <c r="C813" s="6">
-        <v>263.0</v>
+        <v>58.5</v>
       </c>
       <c r="D813" s="7">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="5" t="s">
-        <v>786</v>
+        <v>812</v>
       </c>
       <c r="B814" s="6">
-        <v>281.5</v>
+        <v>68.0</v>
       </c>
       <c r="C814" s="6">
-        <v>241.2</v>
+        <v>65.0</v>
       </c>
       <c r="D814" s="7">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="5" t="s">
-        <v>787</v>
+        <v>813</v>
       </c>
       <c r="B815" s="6">
-        <v>786.6</v>
+        <v>82.0</v>
       </c>
       <c r="C815" s="6">
-        <v>757.5</v>
+        <v>78.0</v>
       </c>
       <c r="D815" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="5" t="s">
-        <v>788</v>
+        <v>814</v>
       </c>
       <c r="B816" s="6">
-        <v>180.0</v>
+        <v>52.0</v>
       </c>
       <c r="C816" s="6">
-        <v>162.0</v>
+        <v>49.0</v>
       </c>
       <c r="D816" s="7">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="5" t="s">
-        <v>789</v>
+        <v>815</v>
       </c>
       <c r="B817" s="6">
-        <v>1071.4</v>
+        <v>52.4</v>
       </c>
       <c r="C817" s="6">
-        <v>1011.9</v>
+        <v>50.2</v>
       </c>
       <c r="D817" s="7">
-        <v>2.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="5" t="s">
-        <v>790</v>
+        <v>816</v>
       </c>
       <c r="B818" s="6">
-        <v>680.0</v>
+        <v>60.0</v>
       </c>
       <c r="C818" s="6">
-        <v>660.0</v>
+        <v>56.0</v>
       </c>
       <c r="D818" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="5" t="s">
-        <v>791</v>
+        <v>817</v>
       </c>
       <c r="B819" s="6">
-        <v>3200.0</v>
+        <v>55.0</v>
       </c>
       <c r="C819" s="6">
-        <v>3200.0</v>
+        <v>51.0</v>
       </c>
       <c r="D819" s="7">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="5" t="s">
-        <v>792</v>
+        <v>818</v>
       </c>
       <c r="B820" s="6">
-        <v>100.0</v>
+        <v>110.3</v>
       </c>
       <c r="C820" s="6">
-        <v>80.0</v>
+        <v>107.6</v>
       </c>
       <c r="D820" s="7">
-        <v>3.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="5" t="s">
-        <v>793</v>
+        <v>819</v>
       </c>
       <c r="B821" s="6">
-        <v>1485.0</v>
+        <v>90.6</v>
       </c>
       <c r="C821" s="6">
-        <v>1375.0</v>
+        <v>86.4</v>
       </c>
       <c r="D821" s="7">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="5" t="s">
-        <v>794</v>
+        <v>820</v>
       </c>
       <c r="B822" s="6">
-        <v>781.5</v>
+        <v>102.0</v>
       </c>
       <c r="C822" s="6">
-        <v>721.4</v>
+        <v>96.9</v>
       </c>
       <c r="D822" s="7">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="5" t="s">
-        <v>795</v>
+        <v>821</v>
       </c>
       <c r="B823" s="6">
-        <v>500.0</v>
+        <v>157.3</v>
       </c>
       <c r="C823" s="6">
-        <v>500.0</v>
+        <v>151.2</v>
       </c>
       <c r="D823" s="7">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="5" t="s">
-        <v>796</v>
+        <v>822</v>
       </c>
       <c r="B824" s="6">
-        <v>169.0</v>
+        <v>40.0</v>
       </c>
       <c r="C824" s="6">
-        <v>162.5</v>
+        <v>35.0</v>
       </c>
       <c r="D824" s="7">
-        <v>25.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="5" t="s">
-        <v>797</v>
+        <v>823</v>
       </c>
       <c r="B825" s="6">
-        <v>361.4</v>
+        <v>55.5</v>
       </c>
       <c r="C825" s="6">
-        <v>338.0</v>
+        <v>52.1</v>
       </c>
       <c r="D825" s="7">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="5" t="s">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="B826" s="6">
-        <v>3213.3</v>
+        <v>51.0</v>
       </c>
       <c r="C826" s="6">
-        <v>2983.8</v>
+        <v>48.0</v>
       </c>
       <c r="D826" s="7">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="5" t="s">
-        <v>799</v>
+        <v>825</v>
       </c>
       <c r="B827" s="6">
-        <v>3080.0</v>
+        <v>45.0</v>
       </c>
       <c r="C827" s="6">
-        <v>3080.0</v>
+        <v>42.0</v>
       </c>
       <c r="D827" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="5" t="s">
-        <v>800</v>
+        <v>826</v>
       </c>
       <c r="B828" s="6">
-        <v>473.5</v>
+        <v>67.9</v>
       </c>
       <c r="C828" s="6">
-        <v>439.7</v>
+        <v>66.5</v>
       </c>
       <c r="D828" s="7">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="5" t="s">
-        <v>801</v>
+        <v>827</v>
       </c>
       <c r="B829" s="6">
-        <v>184.7</v>
+        <v>260.0</v>
       </c>
       <c r="C829" s="6">
-        <v>155.6</v>
+        <v>250.0</v>
       </c>
       <c r="D829" s="7">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="5" t="s">
-        <v>802</v>
+        <v>828</v>
       </c>
       <c r="B830" s="6">
-        <v>450.0</v>
+        <v>139.7</v>
       </c>
       <c r="C830" s="6">
-        <v>420.0</v>
+        <v>129.7</v>
       </c>
       <c r="D830" s="7">
-        <v>50.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="5" t="s">
-        <v>803</v>
+        <v>829</v>
       </c>
       <c r="B831" s="6">
-        <v>630.0</v>
+        <v>250.0</v>
       </c>
       <c r="C831" s="6">
-        <v>600.0</v>
+        <v>230.0</v>
       </c>
       <c r="D831" s="7">
-        <v>50.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="5" t="s">
-        <v>804</v>
+        <v>830</v>
       </c>
       <c r="B832" s="6">
-        <v>135.2</v>
+        <v>25.0</v>
       </c>
       <c r="C832" s="6">
-        <v>127.4</v>
+        <v>230.0</v>
       </c>
       <c r="D832" s="7">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="5" t="s">
-        <v>805</v>
+        <v>831</v>
       </c>
       <c r="B833" s="6">
-        <v>905.4</v>
-      </c>
-      <c r="C833" s="6"/>
+        <v>1414.3</v>
+      </c>
+      <c r="C833" s="6">
+        <v>1414.3</v>
+      </c>
       <c r="D833" s="7">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="834" ht="15.75" customHeight="1">
       <c r="A834" s="5" t="s">
-        <v>806</v>
+        <v>832</v>
       </c>
       <c r="B834" s="6">
-        <v>1500.0</v>
+        <v>87.6</v>
       </c>
       <c r="C834" s="6">
-        <v>1500.0</v>
+        <v>81.1</v>
       </c>
       <c r="D834" s="7">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="835" ht="15.75" customHeight="1">
       <c r="A835" s="5" t="s">
-        <v>807</v>
+        <v>833</v>
       </c>
       <c r="B835" s="6">
-        <v>1600.0</v>
+        <v>103.6</v>
       </c>
       <c r="C835" s="6">
-        <v>1600.0</v>
+        <v>96.2</v>
       </c>
       <c r="D835" s="7">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="836" ht="15.75" customHeight="1">
       <c r="A836" s="5" t="s">
-        <v>808</v>
+        <v>834</v>
       </c>
       <c r="B836" s="6">
-        <v>325.8</v>
+        <v>110.7</v>
       </c>
       <c r="C836" s="6">
-        <v>293.2</v>
+        <v>102.5</v>
       </c>
       <c r="D836" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="837" ht="15.75" customHeight="1">
       <c r="A837" s="5" t="s">
-        <v>809</v>
+        <v>835</v>
       </c>
       <c r="B837" s="6">
-        <v>1200.0</v>
+        <v>134.3</v>
       </c>
       <c r="C837" s="6">
-        <v>1200.0</v>
+        <v>127.2</v>
       </c>
       <c r="D837" s="7">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="838" ht="15.75" customHeight="1">
       <c r="A838" s="5" t="s">
-        <v>810</v>
+        <v>836</v>
       </c>
       <c r="B838" s="6">
-        <v>617.0</v>
+        <v>162.0</v>
       </c>
       <c r="C838" s="6">
-        <v>567.6</v>
+        <v>150.0</v>
       </c>
       <c r="D838" s="7">
-        <v>3.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="839" ht="15.75" customHeight="1">
       <c r="A839" s="5" t="s">
-        <v>811</v>
+        <v>837</v>
       </c>
       <c r="B839" s="6">
-        <v>521.3</v>
+        <v>234.6</v>
       </c>
       <c r="C839" s="6">
-        <v>488.7</v>
+        <v>221.0</v>
       </c>
       <c r="D839" s="7">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="840" ht="15.75" customHeight="1">
       <c r="A840" s="5" t="s">
-        <v>812</v>
+        <v>838</v>
       </c>
       <c r="B840" s="6">
-        <v>195.0</v>
+        <v>234.6</v>
       </c>
       <c r="C840" s="6">
-        <v>187.5</v>
+        <v>221.0</v>
       </c>
       <c r="D840" s="7">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="841" ht="15.75" customHeight="1">
       <c r="A841" s="5" t="s">
-        <v>813</v>
+        <v>839</v>
       </c>
       <c r="B841" s="6">
-        <v>63.0</v>
+        <v>199.8</v>
       </c>
       <c r="C841" s="6">
-        <v>58.5</v>
+        <v>192.4</v>
       </c>
       <c r="D841" s="7">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="842" ht="15.75" customHeight="1">
       <c r="A842" s="5" t="s">
-        <v>814</v>
+        <v>840</v>
       </c>
       <c r="B842" s="6">
-        <v>68.0</v>
+        <v>496.0</v>
       </c>
       <c r="C842" s="6">
-        <v>65.0</v>
+        <v>496.0</v>
       </c>
       <c r="D842" s="7">
-        <v>100.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="843" ht="15.75" customHeight="1">
       <c r="A843" s="5" t="s">
-        <v>815</v>
+        <v>841</v>
       </c>
       <c r="B843" s="6">
-        <v>82.0</v>
+        <v>640.0</v>
       </c>
       <c r="C843" s="6">
-        <v>78.0</v>
+        <v>640.0</v>
       </c>
       <c r="D843" s="7">
-        <v>50.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="844" ht="15.75" customHeight="1">
       <c r="A844" s="5" t="s">
-        <v>816</v>
+        <v>842</v>
       </c>
       <c r="B844" s="6">
-        <v>52.0</v>
+        <v>252.0</v>
       </c>
       <c r="C844" s="6">
-        <v>49.0</v>
+        <v>236.2</v>
       </c>
       <c r="D844" s="7">
-        <v>50.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="845" ht="15.75" customHeight="1">
       <c r="A845" s="5" t="s">
-        <v>817</v>
+        <v>843</v>
       </c>
       <c r="B845" s="6">
-        <v>52.4</v>
+        <v>602.0</v>
       </c>
       <c r="C845" s="6">
-        <v>50.2</v>
+        <v>602.0</v>
       </c>
       <c r="D845" s="7">
-        <v>100.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="846" ht="15.75" customHeight="1">
       <c r="A846" s="5" t="s">
-        <v>818</v>
+        <v>844</v>
       </c>
       <c r="B846" s="6">
-        <v>60.0</v>
+        <v>208.0</v>
       </c>
       <c r="C846" s="6">
-        <v>56.0</v>
+        <v>195.0</v>
       </c>
       <c r="D846" s="7">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="847" ht="15.75" customHeight="1">
       <c r="A847" s="5" t="s">
-        <v>819</v>
+        <v>845</v>
       </c>
       <c r="B847" s="6">
-        <v>55.0</v>
+        <v>362.4</v>
       </c>
       <c r="C847" s="6">
-        <v>51.0</v>
+        <v>339.8</v>
       </c>
       <c r="D847" s="7">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="5" t="s">
-        <v>820</v>
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="848" ht="12.75" customHeight="1">
+      <c r="A848" s="8" t="s">
+        <v>846</v>
       </c>
       <c r="B848" s="6">
-        <v>110.3</v>
+        <v>42.0</v>
       </c>
       <c r="C848" s="6">
-        <v>107.6</v>
+        <v>38.0</v>
       </c>
       <c r="D848" s="7">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="B849" s="6">
-        <v>90.6</v>
-      </c>
-      <c r="C849" s="6">
-        <v>86.4</v>
-      </c>
-      <c r="D849" s="7">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="5" t="s">
-        <v>822</v>
-      </c>
-      <c r="B850" s="6">
-        <v>102.0</v>
-      </c>
-      <c r="C850" s="6">
-        <v>96.9</v>
-      </c>
-      <c r="D850" s="7">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="B851" s="6">
-        <v>157.3</v>
-      </c>
-      <c r="C851" s="6">
-        <v>151.2</v>
-      </c>
-      <c r="D851" s="7">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="5" t="s">
-        <v>824</v>
-      </c>
-      <c r="B852" s="6">
-        <v>40.0</v>
-      </c>
-      <c r="C852" s="6">
-        <v>35.0</v>
-      </c>
-      <c r="D852" s="7">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="B853" s="6">
-        <v>55.5</v>
-      </c>
-      <c r="C853" s="6">
-        <v>52.1</v>
-      </c>
-      <c r="D853" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="B854" s="6">
-        <v>51.0</v>
-      </c>
-      <c r="C854" s="6">
-        <v>48.0</v>
-      </c>
-      <c r="D854" s="7">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="5" t="s">
-        <v>827</v>
-      </c>
-      <c r="B855" s="6">
-        <v>45.0</v>
-      </c>
-      <c r="C855" s="6">
-        <v>42.0</v>
-      </c>
-      <c r="D855" s="7">
         <v>10.0</v>
       </c>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="B856" s="6">
-        <v>67.9</v>
-      </c>
-      <c r="C856" s="6">
-        <v>66.5</v>
-      </c>
-      <c r="D856" s="7">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="5" t="s">
-        <v>829</v>
-      </c>
-      <c r="B857" s="6">
-        <v>260.0</v>
-      </c>
-      <c r="C857" s="6">
-        <v>250.0</v>
-      </c>
-      <c r="D857" s="7">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="5" t="s">
-        <v>830</v>
-      </c>
-      <c r="B858" s="6">
-        <v>139.7</v>
-      </c>
-      <c r="C858" s="6">
-        <v>129.7</v>
-      </c>
-      <c r="D858" s="7">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="5" t="s">
-        <v>831</v>
-      </c>
-      <c r="B859" s="6">
-        <v>250.0</v>
-      </c>
-      <c r="C859" s="6">
-        <v>230.0</v>
-      </c>
-      <c r="D859" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="B860" s="6">
-        <v>25.0</v>
-      </c>
-      <c r="C860" s="6">
-        <v>230.0</v>
-      </c>
-      <c r="D860" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="B861" s="6">
-        <v>1414.3</v>
-      </c>
-      <c r="C861" s="6">
-        <v>1414.3</v>
-      </c>
-      <c r="D861" s="7">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="B862" s="6">
-        <v>87.6</v>
-      </c>
-      <c r="C862" s="6">
-        <v>81.1</v>
-      </c>
-      <c r="D862" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="B863" s="6">
-        <v>103.6</v>
-      </c>
-      <c r="C863" s="6">
-        <v>96.2</v>
-      </c>
-      <c r="D863" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="B864" s="6">
-        <v>110.7</v>
-      </c>
-      <c r="C864" s="6">
-        <v>102.5</v>
-      </c>
-      <c r="D864" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="B865" s="6">
-        <v>134.3</v>
-      </c>
-      <c r="C865" s="6">
-        <v>127.2</v>
-      </c>
-      <c r="D865" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="5" t="s">
-        <v>838</v>
-      </c>
-      <c r="B866" s="6">
-        <v>162.0</v>
-      </c>
-      <c r="C866" s="6">
-        <v>150.0</v>
-      </c>
-      <c r="D866" s="7">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="5" t="s">
-        <v>839</v>
-      </c>
-      <c r="B867" s="6">
-        <v>234.6</v>
-      </c>
-      <c r="C867" s="6">
-        <v>221.0</v>
-      </c>
-      <c r="D867" s="7">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="B868" s="6">
-        <v>234.6</v>
-      </c>
-      <c r="C868" s="6">
-        <v>221.0</v>
-      </c>
-      <c r="D868" s="7">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="B869" s="6">
-        <v>199.8</v>
-      </c>
-      <c r="C869" s="6">
-        <v>192.4</v>
-      </c>
-      <c r="D869" s="7">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="5" t="s">
-        <v>842</v>
-      </c>
-      <c r="B870" s="6">
-        <v>496.0</v>
-      </c>
-      <c r="C870" s="6">
-        <v>496.0</v>
-      </c>
-      <c r="D870" s="7">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="B871" s="6">
-        <v>640.0</v>
-      </c>
-      <c r="C871" s="6">
-        <v>640.0</v>
-      </c>
-      <c r="D871" s="7">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="B872" s="6">
-        <v>252.0</v>
-      </c>
-      <c r="C872" s="6">
-        <v>236.2</v>
-      </c>
-      <c r="D872" s="7">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="B873" s="6">
-        <v>602.0</v>
-      </c>
-      <c r="C873" s="6">
-        <v>602.0</v>
-      </c>
-      <c r="D873" s="7">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="B874" s="6">
-        <v>208.0</v>
-      </c>
-      <c r="C874" s="6">
-        <v>195.0</v>
-      </c>
-      <c r="D874" s="7">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="5" t="s">
+    <row r="849" ht="12.75" customHeight="1">
+      <c r="B849" s="9"/>
+      <c r="C849" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="B875" s="6">
-        <v>362.4</v>
-      </c>
-      <c r="C875" s="6">
-        <v>339.8</v>
-      </c>
-      <c r="D875" s="7">
-        <v>5.0</v>
-      </c>
+    </row>
+    <row r="850" ht="12.75" customHeight="1">
+      <c r="B850" s="9"/>
+      <c r="C850" s="9"/>
+    </row>
+    <row r="851" ht="12.75" customHeight="1">
+      <c r="B851" s="9"/>
+      <c r="C851" s="9"/>
+    </row>
+    <row r="852" ht="12.75" customHeight="1">
+      <c r="B852" s="9"/>
+      <c r="C852" s="9"/>
+    </row>
+    <row r="853" ht="12.75" customHeight="1">
+      <c r="B853" s="9"/>
+      <c r="C853" s="9"/>
+    </row>
+    <row r="854" ht="12.75" customHeight="1">
+      <c r="B854" s="9"/>
+      <c r="C854" s="9"/>
+    </row>
+    <row r="855" ht="12.75" customHeight="1">
+      <c r="B855" s="9"/>
+      <c r="C855" s="9"/>
+    </row>
+    <row r="856" ht="12.75" customHeight="1">
+      <c r="B856" s="9"/>
+      <c r="C856" s="9"/>
+    </row>
+    <row r="857" ht="12.75" customHeight="1">
+      <c r="B857" s="9"/>
+      <c r="C857" s="9"/>
+    </row>
+    <row r="858" ht="12.75" customHeight="1">
+      <c r="B858" s="9"/>
+      <c r="C858" s="9"/>
+    </row>
+    <row r="859" ht="12.75" customHeight="1">
+      <c r="B859" s="9"/>
+      <c r="C859" s="9"/>
+    </row>
+    <row r="860" ht="12.75" customHeight="1">
+      <c r="B860" s="9"/>
+      <c r="C860" s="9"/>
+    </row>
+    <row r="861" ht="12.75" customHeight="1">
+      <c r="B861" s="9"/>
+      <c r="C861" s="9"/>
+    </row>
+    <row r="862" ht="12.75" customHeight="1">
+      <c r="B862" s="9"/>
+      <c r="C862" s="9"/>
+    </row>
+    <row r="863" ht="12.75" customHeight="1">
+      <c r="B863" s="9"/>
+      <c r="C863" s="9"/>
+    </row>
+    <row r="864" ht="12.75" customHeight="1">
+      <c r="B864" s="9"/>
+      <c r="C864" s="9"/>
+    </row>
+    <row r="865" ht="12.75" customHeight="1">
+      <c r="B865" s="9"/>
+      <c r="C865" s="9"/>
+    </row>
+    <row r="866" ht="12.75" customHeight="1">
+      <c r="B866" s="9"/>
+      <c r="C866" s="9"/>
+    </row>
+    <row r="867" ht="12.75" customHeight="1">
+      <c r="B867" s="9"/>
+      <c r="C867" s="9"/>
+    </row>
+    <row r="868" ht="12.75" customHeight="1">
+      <c r="B868" s="9"/>
+      <c r="C868" s="9"/>
+    </row>
+    <row r="869" ht="12.75" customHeight="1">
+      <c r="B869" s="9"/>
+      <c r="C869" s="9"/>
+    </row>
+    <row r="870" ht="12.75" customHeight="1">
+      <c r="B870" s="9"/>
+      <c r="C870" s="9"/>
+    </row>
+    <row r="871" ht="12.75" customHeight="1">
+      <c r="B871" s="9"/>
+      <c r="C871" s="9"/>
+    </row>
+    <row r="872" ht="12.75" customHeight="1">
+      <c r="B872" s="9"/>
+      <c r="C872" s="9"/>
+    </row>
+    <row r="873" ht="12.75" customHeight="1">
+      <c r="B873" s="9"/>
+      <c r="C873" s="9"/>
+    </row>
+    <row r="874" ht="12.75" customHeight="1">
+      <c r="B874" s="9"/>
+      <c r="C874" s="9"/>
+    </row>
+    <row r="875" ht="12.75" customHeight="1">
+      <c r="B875" s="9"/>
+      <c r="C875" s="9"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="A876" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="B876" s="6">
-        <v>42.0</v>
-      </c>
-      <c r="C876" s="6">
-        <v>38.0</v>
-      </c>
-      <c r="D876" s="7">
-        <v>10.0</v>
-      </c>
+      <c r="B876" s="9"/>
+      <c r="C876" s="9"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="B877" s="8"/>
-      <c r="C877" s="9" t="s">
-        <v>849</v>
-      </c>
+      <c r="B877" s="9"/>
+      <c r="C877" s="9"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="B878" s="8"/>
-      <c r="C878" s="8"/>
+      <c r="B878" s="9"/>
+      <c r="C878" s="9"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="B879" s="8"/>
-      <c r="C879" s="8"/>
+      <c r="B879" s="9"/>
+      <c r="C879" s="9"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="B880" s="8"/>
-      <c r="C880" s="8"/>
+      <c r="B880" s="9"/>
+      <c r="C880" s="9"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="B881" s="8"/>
-      <c r="C881" s="8"/>
+      <c r="B881" s="9"/>
+      <c r="C881" s="9"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="B882" s="8"/>
-      <c r="C882" s="8"/>
+      <c r="B882" s="9"/>
+      <c r="C882" s="9"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="B883" s="8"/>
-      <c r="C883" s="8"/>
+      <c r="B883" s="9"/>
+      <c r="C883" s="9"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="B884" s="8"/>
-      <c r="C884" s="8"/>
+      <c r="B884" s="9"/>
+      <c r="C884" s="9"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="B885" s="8"/>
-      <c r="C885" s="8"/>
+      <c r="B885" s="9"/>
+      <c r="C885" s="9"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="B886" s="8"/>
-      <c r="C886" s="8"/>
+      <c r="B886" s="9"/>
+      <c r="C886" s="9"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="B887" s="8"/>
-      <c r="C887" s="8"/>
+      <c r="B887" s="9"/>
+      <c r="C887" s="9"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="B888" s="8"/>
-      <c r="C888" s="8"/>
+      <c r="B888" s="9"/>
+      <c r="C888" s="9"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="B889" s="8"/>
-      <c r="C889" s="8"/>
+      <c r="B889" s="9"/>
+      <c r="C889" s="9"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="B890" s="8"/>
-      <c r="C890" s="8"/>
+      <c r="B890" s="9"/>
+      <c r="C890" s="9"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="B891" s="8"/>
-      <c r="C891" s="8"/>
+      <c r="B891" s="9"/>
+      <c r="C891" s="9"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="B892" s="8"/>
-      <c r="C892" s="8"/>
+      <c r="B892" s="9"/>
+      <c r="C892" s="9"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="B893" s="8"/>
-      <c r="C893" s="8"/>
+      <c r="B893" s="9"/>
+      <c r="C893" s="9"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="B894" s="8"/>
-      <c r="C894" s="8"/>
+      <c r="B894" s="9"/>
+      <c r="C894" s="9"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="B895" s="8"/>
-      <c r="C895" s="8"/>
+      <c r="B895" s="9"/>
+      <c r="C895" s="9"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="B896" s="8"/>
-      <c r="C896" s="8"/>
+      <c r="B896" s="9"/>
+      <c r="C896" s="9"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="B897" s="8"/>
-      <c r="C897" s="8"/>
+      <c r="B897" s="9"/>
+      <c r="C897" s="9"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="B898" s="8"/>
-      <c r="C898" s="8"/>
+      <c r="B898" s="9"/>
+      <c r="C898" s="9"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="B899" s="8"/>
-      <c r="C899" s="8"/>
+      <c r="B899" s="9"/>
+      <c r="C899" s="9"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="B900" s="8"/>
-      <c r="C900" s="8"/>
+      <c r="B900" s="9"/>
+      <c r="C900" s="9"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="B901" s="8"/>
-      <c r="C901" s="8"/>
+      <c r="B901" s="9"/>
+      <c r="C901" s="9"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="B902" s="8"/>
-      <c r="C902" s="8"/>
+      <c r="B902" s="9"/>
+      <c r="C902" s="9"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="B903" s="8"/>
-      <c r="C903" s="8"/>
+      <c r="B903" s="9"/>
+      <c r="C903" s="9"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="B904" s="8"/>
-      <c r="C904" s="8"/>
+      <c r="B904" s="9"/>
+      <c r="C904" s="9"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="B905" s="8"/>
-      <c r="C905" s="8"/>
+      <c r="B905" s="9"/>
+      <c r="C905" s="9"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="B906" s="8"/>
-      <c r="C906" s="8"/>
+      <c r="B906" s="9"/>
+      <c r="C906" s="9"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="B907" s="8"/>
-      <c r="C907" s="8"/>
+      <c r="B907" s="9"/>
+      <c r="C907" s="9"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="B908" s="8"/>
-      <c r="C908" s="8"/>
+      <c r="B908" s="9"/>
+      <c r="C908" s="9"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="B909" s="8"/>
-      <c r="C909" s="8"/>
+      <c r="B909" s="9"/>
+      <c r="C909" s="9"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="B910" s="8"/>
-      <c r="C910" s="8"/>
+      <c r="B910" s="9"/>
+      <c r="C910" s="9"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="B911" s="8"/>
-      <c r="C911" s="8"/>
+      <c r="B911" s="9"/>
+      <c r="C911" s="9"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="B912" s="8"/>
-      <c r="C912" s="8"/>
+      <c r="B912" s="9"/>
+      <c r="C912" s="9"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="B913" s="8"/>
-      <c r="C913" s="8"/>
+      <c r="B913" s="9"/>
+      <c r="C913" s="9"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="B914" s="8"/>
-      <c r="C914" s="8"/>
+      <c r="B914" s="9"/>
+      <c r="C914" s="9"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="B915" s="8"/>
-      <c r="C915" s="8"/>
+      <c r="B915" s="9"/>
+      <c r="C915" s="9"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="B916" s="8"/>
-      <c r="C916" s="8"/>
+      <c r="B916" s="9"/>
+      <c r="C916" s="9"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="B917" s="8"/>
-      <c r="C917" s="8"/>
+      <c r="B917" s="9"/>
+      <c r="C917" s="9"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="B918" s="8"/>
-      <c r="C918" s="8"/>
+      <c r="B918" s="9"/>
+      <c r="C918" s="9"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="B919" s="8"/>
-      <c r="C919" s="8"/>
+      <c r="B919" s="9"/>
+      <c r="C919" s="9"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="B920" s="8"/>
-      <c r="C920" s="8"/>
+      <c r="B920" s="9"/>
+      <c r="C920" s="9"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="B921" s="8"/>
-      <c r="C921" s="8"/>
+      <c r="B921" s="9"/>
+      <c r="C921" s="9"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="B922" s="8"/>
-      <c r="C922" s="8"/>
+      <c r="B922" s="9"/>
+      <c r="C922" s="9"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="B923" s="8"/>
-      <c r="C923" s="8"/>
+      <c r="B923" s="9"/>
+      <c r="C923" s="9"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="B924" s="8"/>
-      <c r="C924" s="8"/>
+      <c r="B924" s="9"/>
+      <c r="C924" s="9"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="B925" s="8"/>
-      <c r="C925" s="8"/>
+      <c r="B925" s="9"/>
+      <c r="C925" s="9"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="B926" s="8"/>
-      <c r="C926" s="8"/>
+      <c r="B926" s="9"/>
+      <c r="C926" s="9"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="B927" s="8"/>
-      <c r="C927" s="8"/>
+      <c r="B927" s="9"/>
+      <c r="C927" s="9"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="B928" s="8"/>
-      <c r="C928" s="8"/>
+      <c r="B928" s="9"/>
+      <c r="C928" s="9"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="B929" s="8"/>
-      <c r="C929" s="8"/>
+      <c r="B929" s="9"/>
+      <c r="C929" s="9"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="B930" s="8"/>
-      <c r="C930" s="8"/>
+      <c r="B930" s="9"/>
+      <c r="C930" s="9"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="B931" s="8"/>
-      <c r="C931" s="8"/>
+      <c r="B931" s="9"/>
+      <c r="C931" s="9"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="B932" s="8"/>
-      <c r="C932" s="8"/>
+      <c r="B932" s="9"/>
+      <c r="C932" s="9"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="B933" s="8"/>
-      <c r="C933" s="8"/>
+      <c r="B933" s="9"/>
+      <c r="C933" s="9"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="B934" s="8"/>
-      <c r="C934" s="8"/>
+      <c r="B934" s="9"/>
+      <c r="C934" s="9"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="B935" s="8"/>
-      <c r="C935" s="8"/>
+      <c r="B935" s="9"/>
+      <c r="C935" s="9"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="B936" s="8"/>
-      <c r="C936" s="8"/>
+      <c r="B936" s="9"/>
+      <c r="C936" s="9"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="B937" s="8"/>
-      <c r="C937" s="8"/>
+      <c r="B937" s="9"/>
+      <c r="C937" s="9"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="B938" s="8"/>
-      <c r="C938" s="8"/>
+      <c r="B938" s="9"/>
+      <c r="C938" s="9"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="B939" s="8"/>
-      <c r="C939" s="8"/>
+      <c r="B939" s="9"/>
+      <c r="C939" s="9"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="B940" s="8"/>
-      <c r="C940" s="8"/>
+      <c r="B940" s="9"/>
+      <c r="C940" s="9"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="B941" s="8"/>
-      <c r="C941" s="8"/>
+      <c r="B941" s="9"/>
+      <c r="C941" s="9"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="B942" s="8"/>
-      <c r="C942" s="8"/>
+      <c r="B942" s="9"/>
+      <c r="C942" s="9"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="B943" s="8"/>
-      <c r="C943" s="8"/>
+      <c r="B943" s="9"/>
+      <c r="C943" s="9"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="B944" s="8"/>
-      <c r="C944" s="8"/>
+      <c r="B944" s="9"/>
+      <c r="C944" s="9"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="B945" s="8"/>
-      <c r="C945" s="8"/>
+      <c r="B945" s="9"/>
+      <c r="C945" s="9"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="B946" s="8"/>
-      <c r="C946" s="8"/>
+      <c r="B946" s="9"/>
+      <c r="C946" s="9"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="B947" s="8"/>
-      <c r="C947" s="8"/>
+      <c r="B947" s="9"/>
+      <c r="C947" s="9"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="B948" s="8"/>
-      <c r="C948" s="8"/>
+      <c r="B948" s="9"/>
+      <c r="C948" s="9"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="B949" s="8"/>
-      <c r="C949" s="8"/>
+      <c r="B949" s="9"/>
+      <c r="C949" s="9"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="B950" s="8"/>
-      <c r="C950" s="8"/>
+      <c r="B950" s="9"/>
+      <c r="C950" s="9"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="B951" s="8"/>
-      <c r="C951" s="8"/>
+      <c r="B951" s="9"/>
+      <c r="C951" s="9"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="B952" s="8"/>
-      <c r="C952" s="8"/>
+      <c r="B952" s="9"/>
+      <c r="C952" s="9"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="B953" s="8"/>
-      <c r="C953" s="8"/>
+      <c r="B953" s="9"/>
+      <c r="C953" s="9"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="B954" s="8"/>
-      <c r="C954" s="8"/>
+      <c r="B954" s="9"/>
+      <c r="C954" s="9"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="B955" s="8"/>
-      <c r="C955" s="8"/>
+      <c r="B955" s="9"/>
+      <c r="C955" s="9"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="B956" s="8"/>
-      <c r="C956" s="8"/>
+      <c r="B956" s="9"/>
+      <c r="C956" s="9"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="B957" s="8"/>
-      <c r="C957" s="8"/>
+      <c r="B957" s="9"/>
+      <c r="C957" s="9"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="B958" s="8"/>
-      <c r="C958" s="8"/>
+      <c r="B958" s="9"/>
+      <c r="C958" s="9"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="B959" s="8"/>
-      <c r="C959" s="8"/>
+      <c r="B959" s="9"/>
+      <c r="C959" s="9"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="B960" s="8"/>
-      <c r="C960" s="8"/>
+      <c r="B960" s="9"/>
+      <c r="C960" s="9"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="B961" s="8"/>
-      <c r="C961" s="8"/>
+      <c r="B961" s="9"/>
+      <c r="C961" s="9"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="B962" s="8"/>
-      <c r="C962" s="8"/>
+      <c r="B962" s="9"/>
+      <c r="C962" s="9"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="B963" s="8"/>
-      <c r="C963" s="8"/>
+      <c r="B963" s="9"/>
+      <c r="C963" s="9"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="B964" s="8"/>
-      <c r="C964" s="8"/>
+      <c r="B964" s="9"/>
+      <c r="C964" s="9"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="B965" s="8"/>
-      <c r="C965" s="8"/>
+      <c r="B965" s="9"/>
+      <c r="C965" s="9"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="B966" s="8"/>
-      <c r="C966" s="8"/>
+      <c r="B966" s="9"/>
+      <c r="C966" s="9"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="B967" s="8"/>
-      <c r="C967" s="8"/>
+      <c r="B967" s="9"/>
+      <c r="C967" s="9"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="B968" s="8"/>
-      <c r="C968" s="8"/>
+      <c r="B968" s="9"/>
+      <c r="C968" s="9"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="B969" s="8"/>
-      <c r="C969" s="8"/>
+      <c r="B969" s="9"/>
+      <c r="C969" s="9"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="B970" s="8"/>
-      <c r="C970" s="8"/>
+      <c r="B970" s="9"/>
+      <c r="C970" s="9"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="B971" s="8"/>
-      <c r="C971" s="8"/>
+      <c r="B971" s="9"/>
+      <c r="C971" s="9"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="B972" s="8"/>
-      <c r="C972" s="8"/>
-    </row>
-    <row r="973" ht="12.75" customHeight="1">
-      <c r="B973" s="8"/>
-      <c r="C973" s="8"/>
-    </row>
-    <row r="974" ht="12.75" customHeight="1">
-      <c r="B974" s="8"/>
-      <c r="C974" s="8"/>
-    </row>
-    <row r="975" ht="12.75" customHeight="1">
-      <c r="B975" s="8"/>
-      <c r="C975" s="8"/>
-    </row>
-    <row r="976" ht="12.75" customHeight="1">
-      <c r="B976" s="8"/>
-      <c r="C976" s="8"/>
-    </row>
-    <row r="977" ht="12.75" customHeight="1">
-      <c r="B977" s="8"/>
-      <c r="C977" s="8"/>
-    </row>
-    <row r="978" ht="12.75" customHeight="1">
-      <c r="B978" s="8"/>
-      <c r="C978" s="8"/>
-    </row>
-    <row r="979" ht="12.75" customHeight="1">
-      <c r="B979" s="8"/>
-      <c r="C979" s="8"/>
-    </row>
-    <row r="980" ht="12.75" customHeight="1">
-      <c r="B980" s="8"/>
-      <c r="C980" s="8"/>
-    </row>
-    <row r="981" ht="12.75" customHeight="1">
-      <c r="B981" s="8"/>
-      <c r="C981" s="8"/>
-    </row>
-    <row r="982" ht="12.75" customHeight="1">
-      <c r="B982" s="8"/>
-      <c r="C982" s="8"/>
-    </row>
-    <row r="983" ht="12.75" customHeight="1">
-      <c r="B983" s="8"/>
-      <c r="C983" s="8"/>
-    </row>
-    <row r="984" ht="12.75" customHeight="1">
-      <c r="B984" s="8"/>
-      <c r="C984" s="8"/>
-    </row>
-    <row r="985" ht="12.75" customHeight="1">
-      <c r="B985" s="8"/>
-      <c r="C985" s="8"/>
-    </row>
-    <row r="986" ht="12.75" customHeight="1">
-      <c r="B986" s="8"/>
-      <c r="C986" s="8"/>
-    </row>
-    <row r="987" ht="12.75" customHeight="1">
-      <c r="B987" s="8"/>
-      <c r="C987" s="8"/>
-    </row>
-    <row r="988" ht="12.75" customHeight="1">
-      <c r="B988" s="8"/>
-      <c r="C988" s="8"/>
-    </row>
-    <row r="989" ht="12.75" customHeight="1">
-      <c r="B989" s="8"/>
-      <c r="C989" s="8"/>
-    </row>
-    <row r="990" ht="12.75" customHeight="1">
-      <c r="B990" s="8"/>
-      <c r="C990" s="8"/>
-    </row>
-    <row r="991" ht="12.75" customHeight="1">
-      <c r="B991" s="8"/>
-      <c r="C991" s="8"/>
-    </row>
-    <row r="992" ht="12.75" customHeight="1">
-      <c r="B992" s="8"/>
-      <c r="C992" s="8"/>
-    </row>
-    <row r="993" ht="12.75" customHeight="1">
-      <c r="B993" s="8"/>
-      <c r="C993" s="8"/>
-    </row>
-    <row r="994" ht="12.75" customHeight="1">
-      <c r="B994" s="8"/>
-      <c r="C994" s="8"/>
-    </row>
-    <row r="995" ht="12.75" customHeight="1">
-      <c r="B995" s="8"/>
-      <c r="C995" s="8"/>
-    </row>
-    <row r="996" ht="12.75" customHeight="1">
-      <c r="B996" s="8"/>
-      <c r="C996" s="8"/>
-    </row>
-    <row r="997" ht="12.75" customHeight="1">
-      <c r="B997" s="8"/>
-      <c r="C997" s="8"/>
-    </row>
-    <row r="998" ht="12.75" customHeight="1">
-      <c r="B998" s="8"/>
-      <c r="C998" s="8"/>
-    </row>
-    <row r="999" ht="12.75" customHeight="1">
-      <c r="B999" s="8"/>
-      <c r="C999" s="8"/>
-    </row>
-    <row r="1000" ht="12.75" customHeight="1">
-      <c r="B1000" s="8"/>
-      <c r="C1000" s="8"/>
+      <c r="B972" s="9"/>
+      <c r="C972" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
